--- a/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:57:11+00:00</t>
+    <t>2026-09-14T07:03:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:03:29+00:00</t>
+    <t>2026-09-14T07:11:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc4</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:11:51+00:00</t>
+    <t>2026-09-14T07:28:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:28:02+00:00</t>
+    <t>2026-09-14T08:01:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T08:01:31+00:00</t>
+    <t>2026-09-14T08:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$195</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7063" uniqueCount="813">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7284" uniqueCount="819">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T08:17:06+00:00</t>
+    <t>2026-10-09T09:59:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1652,10 +1652,10 @@
 </t>
   </si>
   <si>
-    <t>Who is responsible for the observation</t>
-  </si>
-  <si>
-    <t>Who was responsible for asserting the observed value as "true".</t>
+    <t>Durchführendes Labor</t>
+  </si>
+  <si>
+    <t>Organisation (Labor), die die Laboruntersuchung durchgeführt hat.</t>
   </si>
   <si>
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
@@ -1668,6 +1668,24 @@
   </si>
   <si>
     <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>Observation.performer.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.reference</t>
+  </si>
+  <si>
+    <t>Observation.performer.type</t>
+  </si>
+  <si>
+    <t>Observation.performer.identifier</t>
+  </si>
+  <si>
+    <t>Observation.performer.display</t>
   </si>
   <si>
     <t>Observation.value[x]</t>
@@ -2872,7 +2890,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO189"/>
+  <dimension ref="A1:AO195"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="73.328125" customWidth="true" bestFit="true"/>
@@ -15694,7 +15712,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="110" hidden="true">
+    <row r="110">
       <c r="A110" t="s" s="2">
         <v>522</v>
       </c>
@@ -15713,7 +15731,7 @@
         <v>81</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>82</v>
@@ -15830,29 +15848,25 @@
         <v>92</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>531</v>
+        <v>106</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>532</v>
+        <v>107</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>535</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>82</v>
       </c>
@@ -15888,17 +15902,19 @@
         <v>82</v>
       </c>
       <c r="AB111" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="AC111" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>537</v>
+        <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>530</v>
+        <v>109</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15907,71 +15923,67 @@
         <v>92</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>538</v>
+        <v>82</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>539</v>
+        <v>82</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>540</v>
+        <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>541</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="C112" t="s" s="2">
-        <v>543</v>
-      </c>
+        <v>531</v>
+      </c>
+      <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>544</v>
+        <v>112</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>545</v>
+        <v>113</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>546</v>
+        <v>114</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>535</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>82</v>
       </c>
@@ -16007,54 +16019,54 @@
         <v>82</v>
       </c>
       <c r="AB112" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC112" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>530</v>
+        <v>119</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>538</v>
+        <v>82</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>539</v>
+        <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>540</v>
+        <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>541</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="113" hidden="true">
+    <row r="113">
       <c r="A113" t="s" s="2">
-        <v>547</v>
+        <v>532</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>548</v>
+        <v>532</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16068,24 +16080,26 @@
         <v>92</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K113" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>107</v>
+        <v>449</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N113" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>82</v>
@@ -16134,7 +16148,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>109</v>
+        <v>452</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16143,10 +16157,10 @@
         <v>92</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>82</v>
+        <v>453</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>82</v>
@@ -16166,21 +16180,21 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>549</v>
+        <v>533</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>550</v>
+        <v>533</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>82</v>
@@ -16189,19 +16203,19 @@
         <v>82</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>113</v>
+        <v>455</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>114</v>
+        <v>456</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>115</v>
+        <v>457</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16227,43 +16241,43 @@
         <v>82</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>82</v>
+        <v>459</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB114" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC114" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE114" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>119</v>
+        <v>460</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>82</v>
@@ -16281,16 +16295,14 @@
         <v>82</v>
       </c>
     </row>
-    <row r="115" hidden="true">
+    <row r="115">
       <c r="A115" t="s" s="2">
-        <v>551</v>
+        <v>534</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="C115" t="s" s="2">
-        <v>552</v>
-      </c>
+        <v>534</v>
+      </c>
+      <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
         <v>82</v>
       </c>
@@ -16299,28 +16311,28 @@
         <v>80</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>553</v>
+        <v>203</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>554</v>
+        <v>462</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>555</v>
+        <v>463</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>556</v>
+        <v>464</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16370,19 +16382,19 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>119</v>
+        <v>465</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>82</v>
@@ -16400,12 +16412,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>557</v>
+        <v>535</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>558</v>
+        <v>535</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16413,13 +16425,13 @@
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G116" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H116" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I116" t="s" s="2">
         <v>82</v>
@@ -16428,20 +16440,18 @@
         <v>93</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>559</v>
+        <v>106</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>560</v>
+        <v>467</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>561</v>
+        <v>468</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>563</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>82</v>
       </c>
@@ -16489,7 +16499,7 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>564</v>
+        <v>470</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16510,7 +16520,7 @@
         <v>82</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>565</v>
+        <v>82</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>82</v>
@@ -16521,10 +16531,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>566</v>
+        <v>536</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>567</v>
+        <v>536</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16538,25 +16548,29 @@
         <v>92</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I117" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>106</v>
+        <v>537</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>504</v>
+        <v>538</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
+        <v>539</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>541</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>82</v>
       </c>
@@ -16592,19 +16606,17 @@
         <v>82</v>
       </c>
       <c r="AB117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>542</v>
+      </c>
+      <c r="AC117" s="2"/>
       <c r="AD117" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE117" t="s" s="2">
-        <v>82</v>
+        <v>543</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>109</v>
+        <v>536</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16613,35 +16625,37 @@
         <v>92</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>82</v>
+        <v>544</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>82</v>
+        <v>545</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>82</v>
+        <v>546</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>82</v>
+        <v>547</v>
       </c>
     </row>
-    <row r="118" hidden="true">
+    <row r="118">
       <c r="A118" t="s" s="2">
-        <v>568</v>
+        <v>548</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="C118" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>549</v>
+      </c>
       <c r="D118" t="s" s="2">
         <v>82</v>
       </c>
@@ -16650,28 +16664,32 @@
         <v>80</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>112</v>
+        <v>550</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>193</v>
+        <v>551</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N118" s="2"/>
-      <c r="O118" s="2"/>
+        <v>552</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>541</v>
+      </c>
       <c r="P118" t="s" s="2">
         <v>82</v>
       </c>
@@ -16707,56 +16725,56 @@
         <v>82</v>
       </c>
       <c r="AB118" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC118" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE118" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>119</v>
+        <v>536</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>82</v>
+        <v>544</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>82</v>
+        <v>545</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>82</v>
+        <v>546</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>82</v>
+        <v>547</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>570</v>
+        <v>553</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="C119" t="s" s="2">
-        <v>571</v>
-      </c>
+        <v>554</v>
+      </c>
+      <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
         <v>82</v>
       </c>
@@ -16768,7 +16786,7 @@
         <v>92</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>82</v>
@@ -16777,17 +16795,15 @@
         <v>82</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>572</v>
+        <v>106</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>573</v>
+        <v>107</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>575</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>82</v>
@@ -16836,19 +16852,19 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>82</v>
@@ -16857,7 +16873,7 @@
         <v>82</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>229</v>
+        <v>82</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>82</v>
@@ -16868,21 +16884,21 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>576</v>
+        <v>555</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>577</v>
+        <v>556</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>82</v>
@@ -16894,15 +16910,17 @@
         <v>82</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>559</v>
+        <v>112</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>578</v>
+        <v>113</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="N120" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>82</v>
@@ -16939,31 +16957,31 @@
         <v>82</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC120" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD120" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE120" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>579</v>
+        <v>119</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>82</v>
@@ -16981,14 +16999,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>580</v>
+        <v>557</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="C121" s="2"/>
+        <v>556</v>
+      </c>
+      <c r="C121" t="s" s="2">
+        <v>558</v>
+      </c>
       <c r="D121" t="s" s="2">
         <v>82</v>
       </c>
@@ -16997,36 +17017,34 @@
         <v>80</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I121" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>167</v>
+        <v>559</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>582</v>
+        <v>560</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="N121" s="2"/>
-      <c r="O121" t="s" s="2">
-        <v>584</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q121" t="s" s="2">
-        <v>585</v>
-      </c>
+      <c r="Q121" s="2"/>
       <c r="R121" t="s" s="2">
         <v>82</v>
       </c>
@@ -17046,13 +17064,13 @@
         <v>82</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>586</v>
+        <v>82</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>587</v>
+        <v>82</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>82</v>
@@ -17070,19 +17088,19 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>588</v>
+        <v>119</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>82</v>
@@ -17091,7 +17109,7 @@
         <v>82</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>589</v>
+        <v>82</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>82</v>
@@ -17102,10 +17120,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>590</v>
+        <v>563</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>591</v>
+        <v>564</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17128,17 +17146,19 @@
         <v>93</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>106</v>
+        <v>565</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>592</v>
+        <v>566</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="N122" s="2"/>
+        <v>567</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>568</v>
+      </c>
       <c r="O122" t="s" s="2">
-        <v>594</v>
+        <v>569</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>82</v>
@@ -17187,7 +17207,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>595</v>
+        <v>570</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17208,7 +17228,7 @@
         <v>82</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>596</v>
+        <v>571</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>82</v>
@@ -17217,12 +17237,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>597</v>
+        <v>572</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>598</v>
+        <v>573</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17230,39 +17250,37 @@
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G123" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>599</v>
+        <v>504</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>600</v>
+        <v>505</v>
       </c>
       <c r="N123" s="2"/>
-      <c r="O123" t="s" s="2">
-        <v>601</v>
-      </c>
+      <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q123" s="2"/>
       <c r="R123" t="s" s="2">
-        <v>602</v>
+        <v>82</v>
       </c>
       <c r="S123" t="s" s="2">
         <v>82</v>
@@ -17304,7 +17322,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>603</v>
+        <v>109</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17313,10 +17331,10 @@
         <v>92</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>604</v>
+        <v>82</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>82</v>
@@ -17325,7 +17343,7 @@
         <v>82</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>596</v>
+        <v>82</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>82</v>
@@ -17334,12 +17352,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>605</v>
+        <v>574</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>606</v>
+        <v>575</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17347,35 +17365,31 @@
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H124" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>167</v>
+        <v>112</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>607</v>
+        <v>193</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>610</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N124" s="2"/>
+      <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>82</v>
       </c>
@@ -17411,31 +17425,29 @@
         <v>82</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="AC124" s="2"/>
       <c r="AD124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE124" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>611</v>
+        <v>119</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>82</v>
@@ -17444,7 +17456,7 @@
         <v>82</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>596</v>
+        <v>82</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>82</v>
@@ -17455,13 +17467,13 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>612</v>
+        <v>576</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>530</v>
+        <v>575</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>613</v>
+        <v>577</v>
       </c>
       <c r="D125" t="s" s="2">
         <v>82</v>
@@ -17480,23 +17492,21 @@
         <v>82</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>232</v>
+        <v>578</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>545</v>
+        <v>579</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>546</v>
+        <v>580</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>535</v>
-      </c>
+        <v>581</v>
+      </c>
+      <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>82</v>
       </c>
@@ -17520,11 +17530,13 @@
         <v>82</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="Y125" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z125" t="s" s="2">
-        <v>614</v>
+        <v>82</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>82</v>
@@ -17542,42 +17554,42 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>530</v>
+        <v>119</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>538</v>
+        <v>201</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>539</v>
+        <v>82</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>540</v>
+        <v>229</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>541</v>
+        <v>82</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>615</v>
+        <v>582</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>548</v>
+        <v>583</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17600,13 +17612,13 @@
         <v>82</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>106</v>
+        <v>565</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>107</v>
+        <v>584</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>108</v>
+        <v>514</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -17657,7 +17669,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>109</v>
+        <v>585</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17687,50 +17699,52 @@
         <v>82</v>
       </c>
     </row>
-    <row r="127" hidden="true">
+    <row r="127">
       <c r="A127" t="s" s="2">
-        <v>616</v>
+        <v>586</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>550</v>
+        <v>587</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H127" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I127" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>112</v>
+        <v>167</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>113</v>
+        <v>588</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O127" s="2"/>
+        <v>589</v>
+      </c>
+      <c r="N127" s="2"/>
+      <c r="O127" t="s" s="2">
+        <v>590</v>
+      </c>
       <c r="P127" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q127" s="2"/>
+      <c r="Q127" t="s" s="2">
+        <v>591</v>
+      </c>
       <c r="R127" t="s" s="2">
         <v>82</v>
       </c>
@@ -17750,43 +17764,43 @@
         <v>82</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>82</v>
+        <v>592</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>82</v>
+        <v>593</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB127" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC127" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE127" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>119</v>
+        <v>594</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>82</v>
@@ -17795,7 +17809,7 @@
         <v>82</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>82</v>
+        <v>595</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>82</v>
@@ -17806,10 +17820,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>618</v>
+        <v>597</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17820,7 +17834,7 @@
         <v>92</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>93</v>
@@ -17832,19 +17846,17 @@
         <v>93</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>247</v>
+        <v>598</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>82</v>
@@ -17893,13 +17905,13 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>252</v>
+        <v>601</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>82</v>
@@ -17914,7 +17926,7 @@
         <v>82</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>253</v>
+        <v>602</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>82</v>
@@ -17923,12 +17935,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="129" hidden="true">
+    <row r="129">
       <c r="A129" t="s" s="2">
-        <v>619</v>
+        <v>603</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>620</v>
+        <v>604</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17936,37 +17948,39 @@
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G129" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H129" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I129" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>107</v>
+        <v>605</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>108</v>
+        <v>606</v>
       </c>
       <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
+      <c r="O129" t="s" s="2">
+        <v>607</v>
+      </c>
       <c r="P129" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q129" s="2"/>
       <c r="R129" t="s" s="2">
-        <v>82</v>
+        <v>608</v>
       </c>
       <c r="S129" t="s" s="2">
         <v>82</v>
@@ -18008,7 +18022,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>109</v>
+        <v>609</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -18017,10 +18031,10 @@
         <v>92</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>82</v>
+        <v>610</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>82</v>
@@ -18029,7 +18043,7 @@
         <v>82</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>82</v>
+        <v>602</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>82</v>
@@ -18038,46 +18052,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="130" hidden="true">
+    <row r="130">
       <c r="A130" t="s" s="2">
-        <v>621</v>
+        <v>611</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H130" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>112</v>
+        <v>167</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>113</v>
+        <v>613</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>114</v>
+        <v>614</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O130" s="2"/>
+        <v>615</v>
+      </c>
+      <c r="O130" t="s" s="2">
+        <v>616</v>
+      </c>
       <c r="P130" t="s" s="2">
         <v>82</v>
       </c>
@@ -18113,31 +18129,31 @@
         <v>82</v>
       </c>
       <c r="AB130" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC130" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE130" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>119</v>
+        <v>617</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>82</v>
@@ -18146,7 +18162,7 @@
         <v>82</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>82</v>
+        <v>602</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>82</v>
@@ -18157,18 +18173,20 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="C131" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="C131" t="s" s="2">
+        <v>619</v>
+      </c>
       <c r="D131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G131" t="s" s="2">
         <v>92</v>
@@ -18183,19 +18201,19 @@
         <v>93</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>133</v>
+        <v>232</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>262</v>
+        <v>551</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>263</v>
+        <v>552</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>264</v>
+        <v>540</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>265</v>
+        <v>541</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>82</v>
@@ -18220,13 +18238,11 @@
         <v>82</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y131" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="Y131" s="2"/>
       <c r="Z131" t="s" s="2">
-        <v>82</v>
+        <v>620</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>82</v>
@@ -18244,7 +18260,7 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>267</v>
+        <v>536</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18253,7 +18269,7 @@
         <v>92</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>82</v>
+        <v>544</v>
       </c>
       <c r="AJ131" t="s" s="2">
         <v>104</v>
@@ -18262,24 +18278,24 @@
         <v>82</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>82</v>
+        <v>545</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>268</v>
+        <v>546</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>82</v>
+        <v>547</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>626</v>
+        <v>554</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18293,26 +18309,24 @@
         <v>92</v>
       </c>
       <c r="H132" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I132" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K132" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>271</v>
+        <v>107</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N132" s="2"/>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>82</v>
@@ -18361,7 +18375,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>274</v>
+        <v>109</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18373,7 +18387,7 @@
         <v>82</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK132" t="s" s="2">
         <v>82</v>
@@ -18382,7 +18396,7 @@
         <v>82</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>275</v>
+        <v>82</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>82</v>
@@ -18391,46 +18405,46 @@
         <v>82</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>628</v>
+        <v>556</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H133" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>167</v>
+        <v>112</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>278</v>
+        <v>113</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N133" s="2"/>
-      <c r="O133" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>82</v>
       </c>
@@ -18466,31 +18480,31 @@
         <v>82</v>
       </c>
       <c r="AB133" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC133" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE133" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>282</v>
+        <v>119</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>82</v>
@@ -18499,7 +18513,7 @@
         <v>82</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>283</v>
+        <v>82</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>82</v>
@@ -18508,12 +18522,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="134" hidden="true">
+    <row r="134">
       <c r="A134" t="s" s="2">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18521,13 +18535,13 @@
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H134" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I134" t="s" s="2">
         <v>82</v>
@@ -18536,17 +18550,19 @@
         <v>93</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>286</v>
+        <v>247</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N134" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="O134" t="s" s="2">
-        <v>288</v>
+        <v>250</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>82</v>
@@ -18595,13 +18611,13 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>289</v>
+        <v>252</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>82</v>
@@ -18616,7 +18632,7 @@
         <v>82</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>290</v>
+        <v>253</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>82</v>
@@ -18627,10 +18643,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18650,23 +18666,19 @@
         <v>82</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>293</v>
+        <v>106</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>294</v>
+        <v>107</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N135" s="2"/>
+      <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>82</v>
       </c>
@@ -18714,7 +18726,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>298</v>
+        <v>109</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18726,7 +18738,7 @@
         <v>82</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK135" t="s" s="2">
         <v>82</v>
@@ -18735,7 +18747,7 @@
         <v>82</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>299</v>
+        <v>82</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>82</v>
@@ -18746,21 +18758,21 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>82</v>
@@ -18769,23 +18781,21 @@
         <v>82</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>302</v>
+        <v>113</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>303</v>
+        <v>114</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
         <v>82</v>
       </c>
@@ -18821,31 +18831,31 @@
         <v>82</v>
       </c>
       <c r="AB136" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC136" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD136" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE136" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>306</v>
+        <v>119</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK136" t="s" s="2">
         <v>82</v>
@@ -18854,7 +18864,7 @@
         <v>82</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>307</v>
+        <v>82</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>82</v>
@@ -18865,20 +18875,18 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="C137" t="s" s="2">
-        <v>636</v>
-      </c>
+        <v>630</v>
+      </c>
+      <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G137" t="s" s="2">
         <v>92</v>
@@ -18893,19 +18901,19 @@
         <v>93</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>637</v>
+        <v>133</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>545</v>
+        <v>262</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>546</v>
+        <v>263</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>534</v>
+        <v>264</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>535</v>
+        <v>265</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>82</v>
@@ -18954,7 +18962,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>530</v>
+        <v>267</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -18963,7 +18971,7 @@
         <v>92</v>
       </c>
       <c r="AI137" t="s" s="2">
-        <v>538</v>
+        <v>82</v>
       </c>
       <c r="AJ137" t="s" s="2">
         <v>104</v>
@@ -18972,28 +18980,26 @@
         <v>82</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>539</v>
+        <v>82</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>540</v>
+        <v>268</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO137" t="s" s="2">
-        <v>541</v>
+        <v>82</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="C138" t="s" s="2">
-        <v>639</v>
-      </c>
+        <v>632</v>
+      </c>
+      <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
         <v>82</v>
       </c>
@@ -19014,20 +19020,18 @@
         <v>93</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>640</v>
+        <v>106</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>545</v>
+        <v>271</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>546</v>
+        <v>272</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>535</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>82</v>
       </c>
@@ -19075,7 +19079,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>530</v>
+        <v>274</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19084,7 +19088,7 @@
         <v>92</v>
       </c>
       <c r="AI138" t="s" s="2">
-        <v>538</v>
+        <v>82</v>
       </c>
       <c r="AJ138" t="s" s="2">
         <v>104</v>
@@ -19093,24 +19097,24 @@
         <v>82</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>539</v>
+        <v>82</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>540</v>
+        <v>275</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO138" t="s" s="2">
-        <v>541</v>
+        <v>82</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19118,7 +19122,7 @@
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G139" t="s" s="2">
         <v>92</v>
@@ -19130,22 +19134,20 @@
         <v>82</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>232</v>
+        <v>167</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>642</v>
+        <v>278</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>644</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="N139" s="2"/>
       <c r="O139" t="s" s="2">
-        <v>645</v>
+        <v>280</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>82</v>
@@ -19170,13 +19172,13 @@
         <v>82</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="Y139" t="s" s="2">
-        <v>646</v>
+        <v>82</v>
       </c>
       <c r="Z139" t="s" s="2">
-        <v>647</v>
+        <v>82</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>82</v>
@@ -19194,7 +19196,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>641</v>
+        <v>282</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19203,7 +19205,7 @@
         <v>92</v>
       </c>
       <c r="AI139" t="s" s="2">
-        <v>648</v>
+        <v>82</v>
       </c>
       <c r="AJ139" t="s" s="2">
         <v>104</v>
@@ -19215,7 +19217,7 @@
         <v>82</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>229</v>
+        <v>283</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>82</v>
@@ -19224,47 +19226,45 @@
         <v>82</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>649</v>
+        <v>635</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>649</v>
+        <v>636</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>650</v>
+        <v>82</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J140" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="I140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J140" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K140" t="s" s="2">
-        <v>232</v>
+        <v>106</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>651</v>
+        <v>286</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>653</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="N140" s="2"/>
       <c r="O140" t="s" s="2">
-        <v>654</v>
+        <v>288</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>82</v>
@@ -19289,13 +19289,13 @@
         <v>82</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>655</v>
+        <v>82</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>656</v>
+        <v>82</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>82</v>
@@ -19313,13 +19313,13 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>649</v>
+        <v>289</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>82</v>
@@ -19331,24 +19331,24 @@
         <v>82</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>657</v>
+        <v>82</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>658</v>
+        <v>290</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO140" t="s" s="2">
-        <v>659</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>660</v>
+        <v>637</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>660</v>
+        <v>638</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19359,31 +19359,31 @@
         <v>80</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H141" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I141" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J141" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="I141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J141" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K141" t="s" s="2">
-        <v>661</v>
+        <v>293</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>662</v>
+        <v>294</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>663</v>
+        <v>295</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>664</v>
+        <v>296</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>665</v>
+        <v>297</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>82</v>
@@ -19432,13 +19432,13 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>660</v>
+        <v>298</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>82</v>
@@ -19453,7 +19453,7 @@
         <v>82</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>666</v>
+        <v>299</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>82</v>
@@ -19464,10 +19464,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>667</v>
+        <v>639</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>667</v>
+        <v>640</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19478,7 +19478,7 @@
         <v>80</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>82</v>
@@ -19487,21 +19487,23 @@
         <v>82</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>232</v>
+        <v>106</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>668</v>
+        <v>302</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>669</v>
+        <v>303</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="O142" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="O142" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P142" t="s" s="2">
         <v>82</v>
       </c>
@@ -19525,13 +19527,13 @@
         <v>82</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>671</v>
+        <v>82</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>672</v>
+        <v>82</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>82</v>
@@ -19549,7 +19551,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>667</v>
+        <v>306</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19567,26 +19569,28 @@
         <v>82</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>673</v>
+        <v>82</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>674</v>
+        <v>307</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO142" t="s" s="2">
-        <v>675</v>
+        <v>82</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>676</v>
+        <v>641</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="C143" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="C143" t="s" s="2">
+        <v>642</v>
+      </c>
       <c r="D143" t="s" s="2">
         <v>82</v>
       </c>
@@ -19604,22 +19608,22 @@
         <v>82</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>232</v>
+        <v>643</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>677</v>
+        <v>551</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>678</v>
+        <v>552</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>679</v>
+        <v>540</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>680</v>
+        <v>541</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>82</v>
@@ -19644,13 +19648,13 @@
         <v>82</v>
       </c>
       <c r="X143" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="Y143" t="s" s="2">
-        <v>681</v>
+        <v>82</v>
       </c>
       <c r="Z143" t="s" s="2">
-        <v>682</v>
+        <v>82</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>82</v>
@@ -19668,7 +19672,7 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>676</v>
+        <v>536</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19677,7 +19681,7 @@
         <v>92</v>
       </c>
       <c r="AI143" t="s" s="2">
-        <v>82</v>
+        <v>544</v>
       </c>
       <c r="AJ143" t="s" s="2">
         <v>104</v>
@@ -19686,26 +19690,28 @@
         <v>82</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>82</v>
+        <v>545</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>683</v>
+        <v>546</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO143" t="s" s="2">
-        <v>82</v>
+        <v>547</v>
       </c>
     </row>
-    <row r="144" hidden="true">
+    <row r="144">
       <c r="A144" t="s" s="2">
-        <v>684</v>
+        <v>644</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="C144" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="C144" t="s" s="2">
+        <v>645</v>
+      </c>
       <c r="D144" t="s" s="2">
         <v>82</v>
       </c>
@@ -19717,25 +19723,29 @@
         <v>92</v>
       </c>
       <c r="H144" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I144" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J144" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>106</v>
+        <v>646</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>107</v>
+        <v>551</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N144" s="2"/>
-      <c r="O144" s="2"/>
+        <v>552</v>
+      </c>
+      <c r="N144" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="O144" t="s" s="2">
+        <v>541</v>
+      </c>
       <c r="P144" t="s" s="2">
         <v>82</v>
       </c>
@@ -19783,7 +19793,7 @@
         <v>82</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>109</v>
+        <v>536</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -19792,47 +19802,47 @@
         <v>92</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>82</v>
+        <v>544</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK144" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>82</v>
+        <v>545</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>82</v>
+        <v>546</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO144" t="s" s="2">
-        <v>82</v>
+        <v>547</v>
       </c>
     </row>
-    <row r="145" hidden="true">
+    <row r="145">
       <c r="A145" t="s" s="2">
-        <v>685</v>
+        <v>647</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>685</v>
+        <v>647</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H145" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I145" t="s" s="2">
         <v>82</v>
@@ -19841,18 +19851,20 @@
         <v>82</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>112</v>
+        <v>232</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>113</v>
+        <v>648</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>114</v>
+        <v>649</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O145" s="2"/>
+        <v>650</v>
+      </c>
+      <c r="O145" t="s" s="2">
+        <v>651</v>
+      </c>
       <c r="P145" t="s" s="2">
         <v>82</v>
       </c>
@@ -19876,43 +19888,43 @@
         <v>82</v>
       </c>
       <c r="X145" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>82</v>
+        <v>652</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>82</v>
+        <v>653</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB145" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC145" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD145" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE145" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>119</v>
+        <v>647</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>82</v>
+        <v>654</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK145" t="s" s="2">
         <v>82</v>
@@ -19921,7 +19933,7 @@
         <v>82</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>82</v>
+        <v>229</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>82</v>
@@ -19932,14 +19944,14 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>686</v>
+        <v>655</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>686</v>
+        <v>655</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>82</v>
+        <v>656</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
@@ -19955,22 +19967,22 @@
         <v>82</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>145</v>
+        <v>232</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>247</v>
+        <v>657</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>248</v>
+        <v>658</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>249</v>
+        <v>659</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>250</v>
+        <v>660</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>82</v>
@@ -19995,13 +20007,13 @@
         <v>82</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>82</v>
+        <v>661</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>82</v>
+        <v>662</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>82</v>
@@ -20019,7 +20031,7 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>252</v>
+        <v>655</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20037,24 +20049,24 @@
         <v>82</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>82</v>
+        <v>663</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>253</v>
+        <v>664</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO146" t="s" s="2">
-        <v>82</v>
+        <v>665</v>
       </c>
     </row>
-    <row r="147" hidden="true">
+    <row r="147">
       <c r="A147" t="s" s="2">
-        <v>687</v>
+        <v>666</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>687</v>
+        <v>666</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20065,10 +20077,10 @@
         <v>80</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H147" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I147" t="s" s="2">
         <v>82</v>
@@ -20077,16 +20089,20 @@
         <v>82</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>106</v>
+        <v>667</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>107</v>
+        <v>668</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N147" s="2"/>
-      <c r="O147" s="2"/>
+        <v>669</v>
+      </c>
+      <c r="N147" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="O147" t="s" s="2">
+        <v>671</v>
+      </c>
       <c r="P147" t="s" s="2">
         <v>82</v>
       </c>
@@ -20134,19 +20150,19 @@
         <v>82</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>109</v>
+        <v>666</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH147" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI147" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>82</v>
@@ -20155,7 +20171,7 @@
         <v>82</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>82</v>
+        <v>672</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>82</v>
@@ -20166,21 +20182,21 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>688</v>
+        <v>673</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>688</v>
+        <v>673</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G148" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H148" t="s" s="2">
         <v>82</v>
@@ -20192,16 +20208,16 @@
         <v>82</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>112</v>
+        <v>232</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>113</v>
+        <v>674</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>114</v>
+        <v>675</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>115</v>
+        <v>676</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -20227,66 +20243,66 @@
         <v>82</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>82</v>
+        <v>677</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>82</v>
+        <v>678</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB148" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC148" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD148" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE148" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>119</v>
+        <v>673</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH148" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI148" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ148" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK148" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>82</v>
+        <v>679</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>82</v>
+        <v>680</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO148" t="s" s="2">
-        <v>82</v>
+        <v>681</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20294,7 +20310,7 @@
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G149" t="s" s="2">
         <v>92</v>
@@ -20306,22 +20322,22 @@
         <v>82</v>
       </c>
       <c r="J149" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>133</v>
+        <v>232</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>262</v>
+        <v>683</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>263</v>
+        <v>684</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>264</v>
+        <v>685</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>265</v>
+        <v>686</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>82</v>
@@ -20346,13 +20362,13 @@
         <v>82</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>82</v>
+        <v>687</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>82</v>
+        <v>688</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>82</v>
@@ -20370,7 +20386,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>267</v>
+        <v>682</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20391,7 +20407,7 @@
         <v>82</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>268</v>
+        <v>689</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>82</v>
@@ -20425,20 +20441,18 @@
         <v>82</v>
       </c>
       <c r="J150" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K150" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>271</v>
+        <v>107</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N150" s="2"/>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
         <v>82</v>
@@ -20487,7 +20501,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>274</v>
+        <v>109</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20499,7 +20513,7 @@
         <v>82</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK150" t="s" s="2">
         <v>82</v>
@@ -20508,7 +20522,7 @@
         <v>82</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>275</v>
+        <v>82</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>82</v>
@@ -20517,7 +20531,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
         <v>691</v>
       </c>
@@ -20526,37 +20540,37 @@
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H151" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I151" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J151" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>167</v>
+        <v>112</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>278</v>
+        <v>113</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N151" s="2"/>
-      <c r="O151" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="N151" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
         <v>82</v>
       </c>
@@ -20592,31 +20606,31 @@
         <v>82</v>
       </c>
       <c r="AB151" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC151" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD151" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE151" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>282</v>
+        <v>119</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI151" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK151" t="s" s="2">
         <v>82</v>
@@ -20625,7 +20639,7 @@
         <v>82</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>283</v>
+        <v>82</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>82</v>
@@ -20650,7 +20664,7 @@
         <v>80</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H152" t="s" s="2">
         <v>93</v>
@@ -20662,17 +20676,19 @@
         <v>93</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>286</v>
+        <v>247</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N152" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="O152" t="s" s="2">
-        <v>288</v>
+        <v>250</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>82</v>
@@ -20721,13 +20737,13 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>289</v>
+        <v>252</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI152" t="s" s="2">
         <v>82</v>
@@ -20742,7 +20758,7 @@
         <v>82</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>290</v>
+        <v>253</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>82</v>
@@ -20776,23 +20792,19 @@
         <v>82</v>
       </c>
       <c r="J153" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>293</v>
+        <v>106</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>294</v>
+        <v>107</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N153" s="2"/>
+      <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
         <v>82</v>
       </c>
@@ -20840,7 +20852,7 @@
         <v>82</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>298</v>
+        <v>109</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -20852,7 +20864,7 @@
         <v>82</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK153" t="s" s="2">
         <v>82</v>
@@ -20861,7 +20873,7 @@
         <v>82</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>299</v>
+        <v>82</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>82</v>
@@ -20879,14 +20891,14 @@
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H154" t="s" s="2">
         <v>82</v>
@@ -20895,23 +20907,21 @@
         <v>82</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>302</v>
+        <v>113</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>303</v>
+        <v>114</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
         <v>82</v>
       </c>
@@ -20947,31 +20957,31 @@
         <v>82</v>
       </c>
       <c r="AB154" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC154" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD154" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE154" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>306</v>
+        <v>119</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH154" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI154" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK154" t="s" s="2">
         <v>82</v>
@@ -20980,7 +20990,7 @@
         <v>82</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>307</v>
+        <v>82</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>82</v>
@@ -21002,7 +21012,7 @@
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G155" t="s" s="2">
         <v>92</v>
@@ -21014,21 +21024,23 @@
         <v>82</v>
       </c>
       <c r="J155" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>696</v>
+        <v>133</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>697</v>
+        <v>262</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>698</v>
+        <v>263</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="O155" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="O155" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P155" t="s" s="2">
         <v>82</v>
       </c>
@@ -21076,7 +21088,7 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>695</v>
+        <v>267</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -21094,24 +21106,24 @@
         <v>82</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>700</v>
+        <v>82</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>701</v>
+        <v>268</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO155" t="s" s="2">
-        <v>702</v>
+        <v>82</v>
       </c>
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21131,18 +21143,20 @@
         <v>82</v>
       </c>
       <c r="J156" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K156" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>107</v>
+        <v>271</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N156" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N156" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
         <v>82</v>
@@ -21191,7 +21205,7 @@
         <v>82</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>109</v>
+        <v>274</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -21203,7 +21217,7 @@
         <v>82</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK156" t="s" s="2">
         <v>82</v>
@@ -21212,7 +21226,7 @@
         <v>82</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>82</v>
+        <v>275</v>
       </c>
       <c r="AN156" t="s" s="2">
         <v>82</v>
@@ -21221,46 +21235,46 @@
         <v>82</v>
       </c>
     </row>
-    <row r="157" hidden="true">
+    <row r="157">
       <c r="A157" t="s" s="2">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H157" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I157" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>112</v>
+        <v>167</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>113</v>
+        <v>278</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O157" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="N157" s="2"/>
+      <c r="O157" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="P157" t="s" s="2">
         <v>82</v>
       </c>
@@ -21296,31 +21310,31 @@
         <v>82</v>
       </c>
       <c r="AB157" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC157" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD157" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE157" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>119</v>
+        <v>282</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH157" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI157" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK157" t="s" s="2">
         <v>82</v>
@@ -21329,7 +21343,7 @@
         <v>82</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>82</v>
@@ -21340,10 +21354,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21369,15 +21383,15 @@
         <v>106</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>449</v>
+        <v>286</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="O158" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="N158" s="2"/>
+      <c r="O158" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P158" t="s" s="2">
         <v>82</v>
       </c>
@@ -21425,7 +21439,7 @@
         <v>82</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>452</v>
+        <v>289</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -21434,7 +21448,7 @@
         <v>92</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>453</v>
+        <v>82</v>
       </c>
       <c r="AJ158" t="s" s="2">
         <v>104</v>
@@ -21446,7 +21460,7 @@
         <v>82</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>82</v>
@@ -21457,10 +21471,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21483,18 +21497,20 @@
         <v>93</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>133</v>
+        <v>293</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>455</v>
+        <v>294</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>456</v>
+        <v>295</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="O159" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="O159" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="P159" t="s" s="2">
         <v>82</v>
       </c>
@@ -21518,13 +21534,13 @@
         <v>82</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="Y159" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>459</v>
+        <v>82</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>82</v>
@@ -21542,7 +21558,7 @@
         <v>82</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>460</v>
+        <v>298</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -21563,7 +21579,7 @@
         <v>82</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>82</v>
@@ -21572,12 +21588,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21591,7 +21607,7 @@
         <v>92</v>
       </c>
       <c r="H160" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I160" t="s" s="2">
         <v>82</v>
@@ -21600,18 +21616,20 @@
         <v>93</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>203</v>
+        <v>106</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>462</v>
+        <v>302</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>463</v>
+        <v>303</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="O160" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="O160" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P160" t="s" s="2">
         <v>82</v>
       </c>
@@ -21659,7 +21677,7 @@
         <v>82</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>465</v>
+        <v>306</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -21680,7 +21698,7 @@
         <v>82</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>82</v>
+        <v>307</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>82</v>
@@ -21689,12 +21707,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="161" hidden="true">
+    <row r="161">
       <c r="A161" t="s" s="2">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21708,25 +21726,25 @@
         <v>92</v>
       </c>
       <c r="H161" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I161" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J161" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>106</v>
+        <v>702</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>467</v>
+        <v>703</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>468</v>
+        <v>704</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>469</v>
+        <v>705</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
@@ -21776,7 +21794,7 @@
         <v>82</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>470</v>
+        <v>701</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -21794,19 +21812,19 @@
         <v>82</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>82</v>
+        <v>706</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>82</v>
+        <v>707</v>
       </c>
       <c r="AN161" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO161" t="s" s="2">
-        <v>82</v>
+        <v>708</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
         <v>709</v>
       </c>
@@ -21825,7 +21843,7 @@
         <v>92</v>
       </c>
       <c r="H162" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I162" t="s" s="2">
         <v>82</v>
@@ -21834,17 +21852,15 @@
         <v>82</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>710</v>
+        <v>106</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>711</v>
+        <v>107</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="N162" t="s" s="2">
-        <v>713</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N162" s="2"/>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
         <v>82</v>
@@ -21893,7 +21909,7 @@
         <v>82</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>709</v>
+        <v>109</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -21905,41 +21921,41 @@
         <v>82</v>
       </c>
       <c r="AJ162" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK162" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>714</v>
+        <v>82</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>715</v>
+        <v>82</v>
       </c>
       <c r="AN162" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO162" t="s" s="2">
-        <v>716</v>
+        <v>82</v>
       </c>
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E163" s="2"/>
       <c r="F163" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H163" t="s" s="2">
         <v>82</v>
@@ -21951,15 +21967,17 @@
         <v>82</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N163" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N163" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
         <v>82</v>
@@ -21996,31 +22014,31 @@
         <v>82</v>
       </c>
       <c r="AB163" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC163" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD163" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE163" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH163" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI163" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ163" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AK163" t="s" s="2">
         <v>82</v>
@@ -22038,44 +22056,44 @@
         <v>82</v>
       </c>
     </row>
-    <row r="164" hidden="true">
+    <row r="164">
       <c r="A164" t="s" s="2">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E164" s="2"/>
       <c r="F164" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G164" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H164" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I164" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J164" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>113</v>
+        <v>449</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>114</v>
+        <v>450</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>115</v>
+        <v>451</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -22113,31 +22131,31 @@
         <v>82</v>
       </c>
       <c r="AB164" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC164" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD164" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE164" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>119</v>
+        <v>452</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH164" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>82</v>
+        <v>453</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK164" t="s" s="2">
         <v>82</v>
@@ -22155,12 +22173,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22174,7 +22192,7 @@
         <v>92</v>
       </c>
       <c r="H165" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I165" t="s" s="2">
         <v>82</v>
@@ -22183,16 +22201,16 @@
         <v>93</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -22218,13 +22236,13 @@
         <v>82</v>
       </c>
       <c r="X165" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>82</v>
+        <v>459</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>82</v>
@@ -22242,7 +22260,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22251,7 +22269,7 @@
         <v>92</v>
       </c>
       <c r="AI165" t="s" s="2">
-        <v>453</v>
+        <v>82</v>
       </c>
       <c r="AJ165" t="s" s="2">
         <v>104</v>
@@ -22272,12 +22290,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="166" hidden="true">
+    <row r="166">
       <c r="A166" t="s" s="2">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22291,7 +22309,7 @@
         <v>92</v>
       </c>
       <c r="H166" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I166" t="s" s="2">
         <v>82</v>
@@ -22300,16 +22318,16 @@
         <v>93</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>133</v>
+        <v>203</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -22335,13 +22353,13 @@
         <v>82</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>459</v>
+        <v>82</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>82</v>
@@ -22359,7 +22377,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22389,12 +22407,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22408,7 +22426,7 @@
         <v>92</v>
       </c>
       <c r="H167" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I167" t="s" s="2">
         <v>82</v>
@@ -22417,16 +22435,16 @@
         <v>93</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>203</v>
+        <v>106</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -22476,7 +22494,7 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22506,12 +22524,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="168" hidden="true">
+    <row r="168">
       <c r="A168" t="s" s="2">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22525,25 +22543,25 @@
         <v>92</v>
       </c>
       <c r="H168" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I168" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J168" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>106</v>
+        <v>716</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>467</v>
+        <v>717</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>468</v>
+        <v>718</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>469</v>
+        <v>719</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
@@ -22593,7 +22611,7 @@
         <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>470</v>
+        <v>715</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -22611,19 +22629,19 @@
         <v>82</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>82</v>
+        <v>720</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>82</v>
+        <v>721</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>82</v>
+        <v>722</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
         <v>723</v>
       </c>
@@ -22639,10 +22657,10 @@
         <v>80</v>
       </c>
       <c r="G169" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H169" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I169" t="s" s="2">
         <v>82</v>
@@ -22651,20 +22669,16 @@
         <v>82</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>724</v>
+        <v>106</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>725</v>
+        <v>107</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="N169" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="O169" t="s" s="2">
-        <v>728</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N169" s="2"/>
+      <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
         <v>82</v>
       </c>
@@ -22712,19 +22726,19 @@
         <v>82</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>723</v>
+        <v>109</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH169" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI169" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>729</v>
+        <v>82</v>
       </c>
       <c r="AK169" t="s" s="2">
         <v>82</v>
@@ -22733,7 +22747,7 @@
         <v>82</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>730</v>
+        <v>82</v>
       </c>
       <c r="AN169" t="s" s="2">
         <v>82</v>
@@ -22744,21 +22758,21 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G170" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H170" t="s" s="2">
         <v>82</v>
@@ -22770,15 +22784,17 @@
         <v>82</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N170" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N170" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
         <v>82</v>
@@ -22815,31 +22831,31 @@
         <v>82</v>
       </c>
       <c r="AB170" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC170" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD170" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE170" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH170" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI170" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ170" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AK170" t="s" s="2">
         <v>82</v>
@@ -22857,44 +22873,44 @@
         <v>82</v>
       </c>
     </row>
-    <row r="171" hidden="true">
+    <row r="171">
       <c r="A171" t="s" s="2">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G171" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H171" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I171" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J171" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>113</v>
+        <v>449</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>114</v>
+        <v>450</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>115</v>
+        <v>451</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -22944,19 +22960,19 @@
         <v>82</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>119</v>
+        <v>452</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH171" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>82</v>
+        <v>453</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK171" t="s" s="2">
         <v>82</v>
@@ -22976,46 +22992,44 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
-        <v>734</v>
+        <v>82</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G172" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H172" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I172" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J172" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>735</v>
+        <v>455</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>736</v>
+        <v>456</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O172" t="s" s="2">
-        <v>737</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
         <v>82</v>
       </c>
@@ -23039,13 +23053,13 @@
         <v>82</v>
       </c>
       <c r="X172" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="Y172" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="Z172" t="s" s="2">
-        <v>82</v>
+        <v>459</v>
       </c>
       <c r="AA172" t="s" s="2">
         <v>82</v>
@@ -23063,19 +23077,19 @@
         <v>82</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>738</v>
+        <v>460</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH172" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI172" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ172" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK172" t="s" s="2">
         <v>82</v>
@@ -23095,10 +23109,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>739</v>
+        <v>727</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>739</v>
+        <v>727</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23118,18 +23132,20 @@
         <v>82</v>
       </c>
       <c r="J173" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>740</v>
+        <v>203</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>741</v>
+        <v>462</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="N173" s="2"/>
+        <v>463</v>
+      </c>
+      <c r="N173" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
         <v>82</v>
@@ -23178,7 +23194,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>739</v>
+        <v>465</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23187,7 +23203,7 @@
         <v>92</v>
       </c>
       <c r="AI173" t="s" s="2">
-        <v>743</v>
+        <v>82</v>
       </c>
       <c r="AJ173" t="s" s="2">
         <v>104</v>
@@ -23199,7 +23215,7 @@
         <v>82</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>744</v>
+        <v>82</v>
       </c>
       <c r="AN173" t="s" s="2">
         <v>82</v>
@@ -23208,12 +23224,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>745</v>
+        <v>728</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>745</v>
+        <v>728</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23227,24 +23243,26 @@
         <v>92</v>
       </c>
       <c r="H174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J174" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="I174" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J174" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K174" t="s" s="2">
-        <v>740</v>
+        <v>106</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>746</v>
+        <v>467</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>747</v>
-      </c>
-      <c r="N174" s="2"/>
+        <v>468</v>
+      </c>
+      <c r="N174" t="s" s="2">
+        <v>469</v>
+      </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
         <v>82</v>
@@ -23293,7 +23311,7 @@
         <v>82</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>745</v>
+        <v>470</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -23302,7 +23320,7 @@
         <v>92</v>
       </c>
       <c r="AI174" t="s" s="2">
-        <v>743</v>
+        <v>82</v>
       </c>
       <c r="AJ174" t="s" s="2">
         <v>104</v>
@@ -23314,7 +23332,7 @@
         <v>82</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>744</v>
+        <v>82</v>
       </c>
       <c r="AN174" t="s" s="2">
         <v>82</v>
@@ -23323,12 +23341,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="175" hidden="true">
+    <row r="175">
       <c r="A175" t="s" s="2">
-        <v>748</v>
+        <v>729</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>748</v>
+        <v>729</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23339,10 +23357,10 @@
         <v>80</v>
       </c>
       <c r="G175" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H175" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I175" t="s" s="2">
         <v>82</v>
@@ -23351,19 +23369,19 @@
         <v>82</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>232</v>
+        <v>730</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>749</v>
+        <v>731</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>750</v>
+        <v>732</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>751</v>
+        <v>733</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>752</v>
+        <v>734</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>82</v>
@@ -23388,13 +23406,13 @@
         <v>82</v>
       </c>
       <c r="X175" t="s" s="2">
-        <v>171</v>
+        <v>82</v>
       </c>
       <c r="Y175" t="s" s="2">
-        <v>753</v>
+        <v>82</v>
       </c>
       <c r="Z175" t="s" s="2">
-        <v>754</v>
+        <v>82</v>
       </c>
       <c r="AA175" t="s" s="2">
         <v>82</v>
@@ -23412,28 +23430,28 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>748</v>
+        <v>729</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH175" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI175" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ175" t="s" s="2">
-        <v>104</v>
+        <v>735</v>
       </c>
       <c r="AK175" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>755</v>
+        <v>82</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>756</v>
+        <v>736</v>
       </c>
       <c r="AN175" t="s" s="2">
         <v>82</v>
@@ -23444,10 +23462,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>757</v>
+        <v>737</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>757</v>
+        <v>737</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23458,7 +23476,7 @@
         <v>80</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H176" t="s" s="2">
         <v>82</v>
@@ -23470,20 +23488,16 @@
         <v>82</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>232</v>
+        <v>106</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>758</v>
+        <v>107</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="N176" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="O176" t="s" s="2">
-        <v>761</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N176" s="2"/>
+      <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
         <v>82</v>
       </c>
@@ -23507,13 +23521,13 @@
         <v>82</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="Y176" t="s" s="2">
-        <v>762</v>
+        <v>82</v>
       </c>
       <c r="Z176" t="s" s="2">
-        <v>763</v>
+        <v>82</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>82</v>
@@ -23531,28 +23545,28 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>757</v>
+        <v>109</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI176" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK176" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL176" t="s" s="2">
-        <v>755</v>
+        <v>82</v>
       </c>
       <c r="AM176" t="s" s="2">
-        <v>756</v>
+        <v>82</v>
       </c>
       <c r="AN176" t="s" s="2">
         <v>82</v>
@@ -23563,21 +23577,21 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>764</v>
+        <v>738</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>764</v>
+        <v>738</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G177" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H177" t="s" s="2">
         <v>82</v>
@@ -23589,18 +23603,18 @@
         <v>82</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>637</v>
+        <v>112</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>765</v>
+        <v>113</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>766</v>
-      </c>
-      <c r="N177" s="2"/>
-      <c r="O177" t="s" s="2">
-        <v>767</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="N177" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
         <v>82</v>
       </c>
@@ -23648,19 +23662,19 @@
         <v>82</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>764</v>
+        <v>119</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH177" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI177" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK177" t="s" s="2">
         <v>82</v>
@@ -23680,42 +23694,46 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>768</v>
+        <v>739</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>768</v>
+        <v>739</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
-        <v>82</v>
+        <v>740</v>
       </c>
       <c r="E178" s="2"/>
       <c r="F178" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G178" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H178" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I178" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J178" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>769</v>
+        <v>741</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>770</v>
-      </c>
-      <c r="N178" s="2"/>
-      <c r="O178" s="2"/>
+        <v>742</v>
+      </c>
+      <c r="N178" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O178" t="s" s="2">
+        <v>743</v>
+      </c>
       <c r="P178" t="s" s="2">
         <v>82</v>
       </c>
@@ -23763,19 +23781,19 @@
         <v>82</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>768</v>
+        <v>744</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH178" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI178" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK178" t="s" s="2">
         <v>82</v>
@@ -23784,7 +23802,7 @@
         <v>82</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>744</v>
+        <v>82</v>
       </c>
       <c r="AN178" t="s" s="2">
         <v>82</v>
@@ -23793,12 +23811,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="179" hidden="true">
+    <row r="179">
       <c r="A179" t="s" s="2">
-        <v>771</v>
+        <v>745</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>771</v>
+        <v>745</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23809,29 +23827,27 @@
         <v>80</v>
       </c>
       <c r="G179" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H179" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I179" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J179" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>772</v>
+        <v>746</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>773</v>
+        <v>747</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>774</v>
-      </c>
-      <c r="N179" t="s" s="2">
-        <v>775</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="N179" s="2"/>
       <c r="O179" s="2"/>
       <c r="P179" t="s" s="2">
         <v>82</v>
@@ -23880,16 +23896,16 @@
         <v>82</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>771</v>
+        <v>745</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH179" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>82</v>
+        <v>749</v>
       </c>
       <c r="AJ179" t="s" s="2">
         <v>104</v>
@@ -23901,7 +23917,7 @@
         <v>82</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>776</v>
+        <v>750</v>
       </c>
       <c r="AN179" t="s" s="2">
         <v>82</v>
@@ -23910,12 +23926,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="180" hidden="true">
+    <row r="180">
       <c r="A180" t="s" s="2">
-        <v>777</v>
+        <v>751</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>777</v>
+        <v>751</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -23926,29 +23942,27 @@
         <v>80</v>
       </c>
       <c r="G180" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H180" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I180" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J180" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>778</v>
+        <v>746</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>779</v>
+        <v>752</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>780</v>
-      </c>
-      <c r="N180" t="s" s="2">
-        <v>781</v>
-      </c>
+        <v>753</v>
+      </c>
+      <c r="N180" s="2"/>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
         <v>82</v>
@@ -23997,16 +24011,16 @@
         <v>82</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>777</v>
+        <v>751</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH180" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI180" t="s" s="2">
-        <v>82</v>
+        <v>749</v>
       </c>
       <c r="AJ180" t="s" s="2">
         <v>104</v>
@@ -24018,7 +24032,7 @@
         <v>82</v>
       </c>
       <c r="AM180" t="s" s="2">
-        <v>776</v>
+        <v>750</v>
       </c>
       <c r="AN180" t="s" s="2">
         <v>82</v>
@@ -24029,10 +24043,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>782</v>
+        <v>754</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>782</v>
+        <v>754</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24043,7 +24057,7 @@
         <v>80</v>
       </c>
       <c r="G181" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H181" t="s" s="2">
         <v>82</v>
@@ -24052,22 +24066,22 @@
         <v>82</v>
       </c>
       <c r="J181" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>724</v>
+        <v>232</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>783</v>
+        <v>755</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>784</v>
+        <v>756</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>785</v>
+        <v>757</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>786</v>
+        <v>758</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>82</v>
@@ -24092,13 +24106,13 @@
         <v>82</v>
       </c>
       <c r="X181" t="s" s="2">
-        <v>82</v>
+        <v>171</v>
       </c>
       <c r="Y181" t="s" s="2">
-        <v>82</v>
+        <v>759</v>
       </c>
       <c r="Z181" t="s" s="2">
-        <v>82</v>
+        <v>760</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>82</v>
@@ -24116,13 +24130,13 @@
         <v>82</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>782</v>
+        <v>754</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH181" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI181" t="s" s="2">
         <v>82</v>
@@ -24134,10 +24148,10 @@
         <v>82</v>
       </c>
       <c r="AL181" t="s" s="2">
-        <v>82</v>
+        <v>761</v>
       </c>
       <c r="AM181" t="s" s="2">
-        <v>787</v>
+        <v>762</v>
       </c>
       <c r="AN181" t="s" s="2">
         <v>82</v>
@@ -24148,10 +24162,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>788</v>
+        <v>763</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>788</v>
+        <v>763</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24162,7 +24176,7 @@
         <v>80</v>
       </c>
       <c r="G182" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H182" t="s" s="2">
         <v>82</v>
@@ -24174,16 +24188,20 @@
         <v>82</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>106</v>
+        <v>232</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>107</v>
+        <v>764</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N182" s="2"/>
-      <c r="O182" s="2"/>
+        <v>765</v>
+      </c>
+      <c r="N182" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="O182" t="s" s="2">
+        <v>767</v>
+      </c>
       <c r="P182" t="s" s="2">
         <v>82</v>
       </c>
@@ -24207,13 +24225,13 @@
         <v>82</v>
       </c>
       <c r="X182" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="Y182" t="s" s="2">
-        <v>82</v>
+        <v>768</v>
       </c>
       <c r="Z182" t="s" s="2">
-        <v>82</v>
+        <v>769</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>82</v>
@@ -24231,28 +24249,28 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>109</v>
+        <v>763</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH182" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI182" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ182" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK182" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL182" t="s" s="2">
-        <v>82</v>
+        <v>761</v>
       </c>
       <c r="AM182" t="s" s="2">
-        <v>82</v>
+        <v>762</v>
       </c>
       <c r="AN182" t="s" s="2">
         <v>82</v>
@@ -24263,21 +24281,21 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G183" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H183" t="s" s="2">
         <v>82</v>
@@ -24289,18 +24307,18 @@
         <v>82</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>112</v>
+        <v>643</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>113</v>
+        <v>771</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N183" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O183" s="2"/>
+        <v>772</v>
+      </c>
+      <c r="N183" s="2"/>
+      <c r="O183" t="s" s="2">
+        <v>773</v>
+      </c>
       <c r="P183" t="s" s="2">
         <v>82</v>
       </c>
@@ -24348,19 +24366,19 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>119</v>
+        <v>770</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH183" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI183" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ183" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK183" t="s" s="2">
         <v>82</v>
@@ -24380,46 +24398,42 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>790</v>
+        <v>774</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>790</v>
+        <v>774</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
-        <v>734</v>
+        <v>82</v>
       </c>
       <c r="E184" s="2"/>
       <c r="F184" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G184" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H184" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I184" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J184" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>735</v>
+        <v>775</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="N184" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O184" t="s" s="2">
-        <v>737</v>
-      </c>
+        <v>776</v>
+      </c>
+      <c r="N184" s="2"/>
+      <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
         <v>82</v>
       </c>
@@ -24467,19 +24481,19 @@
         <v>82</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>738</v>
+        <v>774</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH184" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI184" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ184" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK184" t="s" s="2">
         <v>82</v>
@@ -24488,7 +24502,7 @@
         <v>82</v>
       </c>
       <c r="AM184" t="s" s="2">
-        <v>82</v>
+        <v>750</v>
       </c>
       <c r="AN184" t="s" s="2">
         <v>82</v>
@@ -24499,10 +24513,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>791</v>
+        <v>777</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>791</v>
+        <v>777</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24510,10 +24524,10 @@
       </c>
       <c r="E185" s="2"/>
       <c r="F185" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G185" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H185" t="s" s="2">
         <v>82</v>
@@ -24525,20 +24539,18 @@
         <v>93</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>232</v>
+        <v>778</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>792</v>
+        <v>779</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>793</v>
+        <v>780</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>794</v>
-      </c>
-      <c r="O185" t="s" s="2">
-        <v>406</v>
-      </c>
+        <v>781</v>
+      </c>
+      <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
         <v>82</v>
       </c>
@@ -24562,13 +24574,13 @@
         <v>82</v>
       </c>
       <c r="X185" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="Y185" t="s" s="2">
-        <v>407</v>
+        <v>82</v>
       </c>
       <c r="Z185" t="s" s="2">
-        <v>408</v>
+        <v>82</v>
       </c>
       <c r="AA185" t="s" s="2">
         <v>82</v>
@@ -24586,13 +24598,13 @@
         <v>82</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>791</v>
+        <v>777</v>
       </c>
       <c r="AG185" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH185" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI185" t="s" s="2">
         <v>82</v>
@@ -24604,13 +24616,13 @@
         <v>82</v>
       </c>
       <c r="AL185" t="s" s="2">
-        <v>795</v>
+        <v>82</v>
       </c>
       <c r="AM185" t="s" s="2">
-        <v>411</v>
+        <v>782</v>
       </c>
       <c r="AN185" t="s" s="2">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="AO185" t="s" s="2">
         <v>82</v>
@@ -24618,10 +24630,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>796</v>
+        <v>783</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>796</v>
+        <v>783</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -24632,7 +24644,7 @@
         <v>80</v>
       </c>
       <c r="G186" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H186" t="s" s="2">
         <v>82</v>
@@ -24644,20 +24656,18 @@
         <v>93</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>797</v>
+        <v>784</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>798</v>
+        <v>785</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>546</v>
+        <v>786</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>799</v>
-      </c>
-      <c r="O186" t="s" s="2">
-        <v>535</v>
-      </c>
+        <v>787</v>
+      </c>
+      <c r="O186" s="2"/>
       <c r="P186" t="s" s="2">
         <v>82</v>
       </c>
@@ -24705,13 +24715,13 @@
         <v>82</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>796</v>
+        <v>783</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH186" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI186" t="s" s="2">
         <v>82</v>
@@ -24723,24 +24733,24 @@
         <v>82</v>
       </c>
       <c r="AL186" t="s" s="2">
-        <v>800</v>
+        <v>82</v>
       </c>
       <c r="AM186" t="s" s="2">
-        <v>540</v>
+        <v>782</v>
       </c>
       <c r="AN186" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO186" t="s" s="2">
-        <v>541</v>
+        <v>82</v>
       </c>
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>801</v>
+        <v>788</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>801</v>
+        <v>788</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -24751,7 +24761,7 @@
         <v>80</v>
       </c>
       <c r="G187" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H187" t="s" s="2">
         <v>82</v>
@@ -24760,22 +24770,22 @@
         <v>82</v>
       </c>
       <c r="J187" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>232</v>
+        <v>730</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>802</v>
+        <v>789</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>803</v>
+        <v>790</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>804</v>
+        <v>791</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>645</v>
+        <v>792</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>82</v>
@@ -24800,13 +24810,13 @@
         <v>82</v>
       </c>
       <c r="X187" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="Y187" t="s" s="2">
-        <v>646</v>
+        <v>82</v>
       </c>
       <c r="Z187" t="s" s="2">
-        <v>647</v>
+        <v>82</v>
       </c>
       <c r="AA187" t="s" s="2">
         <v>82</v>
@@ -24824,16 +24834,16 @@
         <v>82</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>801</v>
+        <v>788</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH187" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI187" t="s" s="2">
-        <v>648</v>
+        <v>82</v>
       </c>
       <c r="AJ187" t="s" s="2">
         <v>104</v>
@@ -24845,7 +24855,7 @@
         <v>82</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>229</v>
+        <v>793</v>
       </c>
       <c r="AN187" t="s" s="2">
         <v>82</v>
@@ -24856,21 +24866,21 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>805</v>
+        <v>794</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>805</v>
+        <v>794</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
-        <v>650</v>
+        <v>82</v>
       </c>
       <c r="E188" s="2"/>
       <c r="F188" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G188" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H188" t="s" s="2">
         <v>82</v>
@@ -24882,20 +24892,16 @@
         <v>82</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>232</v>
+        <v>106</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>806</v>
+        <v>107</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>807</v>
-      </c>
-      <c r="N188" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="O188" t="s" s="2">
-        <v>654</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N188" s="2"/>
+      <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
         <v>82</v>
       </c>
@@ -24919,13 +24925,13 @@
         <v>82</v>
       </c>
       <c r="X188" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="Y188" t="s" s="2">
-        <v>808</v>
+        <v>82</v>
       </c>
       <c r="Z188" t="s" s="2">
-        <v>809</v>
+        <v>82</v>
       </c>
       <c r="AA188" t="s" s="2">
         <v>82</v>
@@ -24943,46 +24949,46 @@
         <v>82</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>805</v>
+        <v>109</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH188" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI188" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ188" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK188" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>657</v>
+        <v>82</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>658</v>
+        <v>82</v>
       </c>
       <c r="AN188" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO188" t="s" s="2">
-        <v>659</v>
+        <v>82</v>
       </c>
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>810</v>
+        <v>795</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>810</v>
+        <v>795</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E189" s="2"/>
       <c r="F189" t="s" s="2">
@@ -25001,20 +25007,18 @@
         <v>82</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>811</v>
+        <v>113</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>812</v>
+        <v>114</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="O189" t="s" s="2">
-        <v>728</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O189" s="2"/>
       <c r="P189" t="s" s="2">
         <v>82</v>
       </c>
@@ -25062,7 +25066,7 @@
         <v>82</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>810</v>
+        <v>119</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>80</v>
@@ -25074,26 +25078,740 @@
         <v>82</v>
       </c>
       <c r="AJ189" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO189" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="190" hidden="true">
+      <c r="A190" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="B190" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="C190" s="2"/>
+      <c r="D190" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="E190" s="2"/>
+      <c r="F190" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I190" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="J190" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K190" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L190" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="M190" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="N190" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O190" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="P190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q190" s="2"/>
+      <c r="R190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF190" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="AG190" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH190" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ190" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO190" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="191" hidden="true">
+      <c r="A191" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="B191" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="C191" s="2"/>
+      <c r="D191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E191" s="2"/>
+      <c r="F191" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G191" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J191" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K191" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L191" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="M191" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="N191" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="O191" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="P191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q191" s="2"/>
+      <c r="R191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X191" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="Y191" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="Z191" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AA191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF191" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="AG191" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AH191" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ191" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="AK189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM189" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="AN189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO189" t="s" s="2">
+      <c r="AK191" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL191" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="AM191" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AN191" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AO191" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="192" hidden="true">
+      <c r="A192" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="B192" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="C192" s="2"/>
+      <c r="D192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E192" s="2"/>
+      <c r="F192" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G192" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J192" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K192" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="L192" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="M192" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="N192" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="O192" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="P192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q192" s="2"/>
+      <c r="R192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF192" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="AG192" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH192" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ192" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL192" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="AM192" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AN192" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO192" t="s" s="2">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="193" hidden="true">
+      <c r="A193" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="B193" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="C193" s="2"/>
+      <c r="D193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E193" s="2"/>
+      <c r="F193" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G193" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K193" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L193" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="M193" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="N193" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="O193" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="P193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q193" s="2"/>
+      <c r="R193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X193" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="Y193" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="Z193" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AA193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF193" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="AG193" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH193" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI193" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="AJ193" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM193" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AN193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO193" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="194" hidden="true">
+      <c r="A194" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="B194" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="C194" s="2"/>
+      <c r="D194" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="E194" s="2"/>
+      <c r="F194" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K194" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L194" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="M194" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="N194" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="O194" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="P194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q194" s="2"/>
+      <c r="R194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X194" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="Y194" t="s" s="2">
+        <v>814</v>
+      </c>
+      <c r="Z194" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="AA194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF194" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="AG194" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ194" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL194" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="AM194" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="AN194" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO194" t="s" s="2">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="195" hidden="true">
+      <c r="A195" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="B195" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="C195" s="2"/>
+      <c r="D195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E195" s="2"/>
+      <c r="F195" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G195" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K195" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L195" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="M195" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="N195" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="O195" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="P195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q195" s="2"/>
+      <c r="R195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF195" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="AG195" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH195" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ195" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM195" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="AN195" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO195" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO189">
+  <autoFilter ref="A1:AO195">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -25103,7 +25821,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI188">
+  <conditionalFormatting sqref="A2:AI194">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ci</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T09:59:07+00:00</t>
+    <t>2026-10-09T10:28:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T10:28:47+00:00</t>
+    <t>2026-10-09T10:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$195</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$194</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7284" uniqueCount="819">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7250" uniqueCount="816">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T10:42:14+00:00</t>
+    <t>2026-10-13T11:58:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1558,14 +1558,14 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">dateTime
-</t>
+    <t>dateTime
+Period</t>
   </si>
   <si>
     <t>Untersuchungszeitpunkt</t>
   </si>
   <si>
-    <t>Klinischer Bezugszeitpunkt der Laboruntersuchung</t>
+    <t>Klinischer Bezugszeitpunkt der Laboruntersuchung; ein Zeitraum, wenn die Probe über einen Zeitraum gewonnen wurde, z. B. 24-Stunden-Sammelurin.</t>
   </si>
   <si>
     <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
@@ -1590,12 +1590,6 @@
     <t>Observation.effective[x].id</t>
   </si>
   <si>
-    <t>xml:id (or equivalent in JSON)</t>
-  </si>
-  <si>
-    <t>unique id for the element within a resource (for internal references)</t>
-  </si>
-  <si>
     <t>Observation.effective[x].extension</t>
   </si>
   <si>
@@ -1615,18 +1609,6 @@
     <t>Datum der Probenentnahme | Datum des Eingangs der Probe im Labor</t>
   </si>
   <si>
-    <t>Observation.effective[x].value</t>
-  </si>
-  <si>
-    <t>Primitive value for dateTime</t>
-  </si>
-  <si>
-    <t>The actual value</t>
-  </si>
-  <si>
-    <t>dateTime.value</t>
-  </si>
-  <si>
     <t>Observation.issued</t>
   </si>
   <si>
@@ -1809,6 +1791,12 @@
     <t>Observation.value[x].value.id</t>
   </si>
   <si>
+    <t>xml:id (or equivalent in JSON)</t>
+  </si>
+  <si>
+    <t>unique id for the element within a resource (for internal references)</t>
+  </si>
+  <si>
     <t>Observation.value[x]:valueQuantity.value.extension</t>
   </si>
   <si>
@@ -1841,6 +1829,9 @@
   </si>
   <si>
     <t>Primitive value for decimal</t>
+  </si>
+  <si>
+    <t>The actual value</t>
   </si>
   <si>
     <t>decimal.value</t>
@@ -2890,7 +2881,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO195"/>
+  <dimension ref="A1:AO194"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="73.328125" customWidth="true" bestFit="true"/>
@@ -15166,10 +15157,10 @@
         <v>106</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>504</v>
+        <v>107</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>505</v>
+        <v>108</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -15252,14 +15243,14 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -15281,12 +15272,14 @@
         <v>112</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>193</v>
+        <v>113</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N106" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -15325,7 +15318,9 @@
       <c r="AB106" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="AC106" s="2"/>
+      <c r="AC106" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="AD106" t="s" s="2">
         <v>82</v>
       </c>
@@ -15365,13 +15360,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B107" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="C107" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="C107" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>82</v>
@@ -15393,13 +15388,13 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="L107" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15459,7 +15454,7 @@
         <v>81</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>120</v>
@@ -15480,12 +15475,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="108" hidden="true">
+    <row r="108">
       <c r="A108" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15499,24 +15494,26 @@
         <v>92</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>494</v>
+        <v>127</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="N108" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="M108" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -15565,31 +15562,31 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AN108" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="AG108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH108" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15611,7 +15608,7 @@
         <v>80</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>93</v>
@@ -15623,18 +15620,18 @@
         <v>93</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>127</v>
+        <v>517</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N109" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="O109" s="2"/>
+      <c r="N109" s="2"/>
+      <c r="O109" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
       </c>
@@ -15688,7 +15685,7 @@
         <v>80</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>82</v>
@@ -15697,27 +15694,27 @@
         <v>104</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15728,30 +15725,28 @@
         <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>523</v>
+        <v>106</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>524</v>
+        <v>107</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>525</v>
+        <v>108</v>
       </c>
       <c r="N110" s="2"/>
-      <c r="O110" t="s" s="2">
-        <v>526</v>
-      </c>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>82</v>
       </c>
@@ -15799,31 +15794,31 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>522</v>
+        <v>109</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>527</v>
+        <v>82</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>529</v>
+        <v>82</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -15831,21 +15826,21 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>82</v>
@@ -15857,15 +15852,17 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N111" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15902,31 +15899,31 @@
         <v>82</v>
       </c>
       <c r="AB111" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC111" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>82</v>
@@ -15944,44 +15941,44 @@
         <v>82</v>
       </c>
     </row>
-    <row r="112" hidden="true">
+    <row r="112">
       <c r="A112" t="s" s="2">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>113</v>
+        <v>449</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>114</v>
+        <v>450</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>115</v>
+        <v>451</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -16019,31 +16016,31 @@
         <v>82</v>
       </c>
       <c r="AB112" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC112" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>119</v>
+        <v>452</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>82</v>
+        <v>453</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>82</v>
@@ -16061,12 +16058,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16080,7 +16077,7 @@
         <v>92</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>82</v>
@@ -16089,16 +16086,16 @@
         <v>93</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16124,13 +16121,13 @@
         <v>82</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>82</v>
+        <v>459</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>82</v>
@@ -16148,7 +16145,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16157,7 +16154,7 @@
         <v>92</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>453</v>
+        <v>82</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>104</v>
@@ -16178,12 +16175,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="114" hidden="true">
+    <row r="114">
       <c r="A114" t="s" s="2">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16197,7 +16194,7 @@
         <v>92</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>82</v>
@@ -16206,16 +16203,16 @@
         <v>93</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>133</v>
+        <v>203</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16241,13 +16238,13 @@
         <v>82</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>459</v>
+        <v>82</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>82</v>
@@ -16265,7 +16262,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16295,12 +16292,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16314,7 +16311,7 @@
         <v>92</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>82</v>
@@ -16323,16 +16320,16 @@
         <v>93</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>203</v>
+        <v>106</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16382,7 +16379,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16414,10 +16411,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16431,7 +16428,7 @@
         <v>92</v>
       </c>
       <c r="H116" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I116" t="s" s="2">
         <v>82</v>
@@ -16440,18 +16437,20 @@
         <v>93</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>106</v>
+        <v>531</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>467</v>
+        <v>532</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>468</v>
+        <v>533</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="O116" s="2"/>
+        <v>534</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>82</v>
       </c>
@@ -16487,19 +16486,17 @@
         <v>82</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>536</v>
+      </c>
+      <c r="AC116" s="2"/>
       <c r="AD116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE116" t="s" s="2">
-        <v>82</v>
+        <v>537</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>470</v>
+        <v>530</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16508,7 +16505,7 @@
         <v>92</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>82</v>
+        <v>538</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>104</v>
@@ -16517,26 +16514,28 @@
         <v>82</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>82</v>
+        <v>539</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>82</v>
+        <v>540</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>82</v>
+        <v>541</v>
       </c>
     </row>
-    <row r="117" hidden="true">
+    <row r="117">
       <c r="A117" t="s" s="2">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="C117" s="2"/>
+        <v>530</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>543</v>
+      </c>
       <c r="D117" t="s" s="2">
         <v>82</v>
       </c>
@@ -16557,19 +16556,19 @@
         <v>93</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>82</v>
@@ -16606,17 +16605,19 @@
         <v>82</v>
       </c>
       <c r="AB117" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="AC117" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD117" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE117" t="s" s="2">
-        <v>543</v>
+        <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16625,7 +16626,7 @@
         <v>92</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>104</v>
@@ -16634,28 +16635,26 @@
         <v>82</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO117" t="s" s="2">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="118" hidden="true">
+      <c r="A118" t="s" s="2">
         <v>547</v>
       </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s" s="2">
+      <c r="B118" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="B118" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="C118" t="s" s="2">
-        <v>549</v>
-      </c>
+      <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
         <v>82</v>
       </c>
@@ -16667,29 +16666,25 @@
         <v>92</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>550</v>
+        <v>106</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>551</v>
+        <v>107</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>541</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N118" s="2"/>
+      <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>82</v>
       </c>
@@ -16737,7 +16732,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>536</v>
+        <v>109</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16746,44 +16741,44 @@
         <v>92</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>544</v>
+        <v>82</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>545</v>
+        <v>82</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>547</v>
+        <v>82</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>82</v>
@@ -16795,15 +16790,17 @@
         <v>82</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N119" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>82</v>
@@ -16840,31 +16837,31 @@
         <v>82</v>
       </c>
       <c r="AB119" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC119" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD119" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE119" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>82</v>
@@ -16884,14 +16881,16 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="C120" s="2"/>
+        <v>550</v>
+      </c>
+      <c r="C120" t="s" s="2">
+        <v>552</v>
+      </c>
       <c r="D120" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -16910,16 +16909,16 @@
         <v>82</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>112</v>
+        <v>553</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>113</v>
+        <v>554</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>114</v>
+        <v>555</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>115</v>
+        <v>556</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -16957,16 +16956,16 @@
         <v>82</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC120" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD120" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE120" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
         <v>119</v>
@@ -16999,34 +16998,32 @@
         <v>82</v>
       </c>
     </row>
-    <row r="121" hidden="true">
+    <row r="121">
       <c r="A121" t="s" s="2">
         <v>557</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="C121" t="s" s="2">
         <v>558</v>
       </c>
+      <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K121" t="s" s="2">
         <v>559</v>
@@ -17040,7 +17037,9 @@
       <c r="N121" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="O121" s="2"/>
+      <c r="O121" t="s" s="2">
+        <v>563</v>
+      </c>
       <c r="P121" t="s" s="2">
         <v>82</v>
       </c>
@@ -17088,19 +17087,19 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>119</v>
+        <v>564</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>82</v>
@@ -17109,7 +17108,7 @@
         <v>82</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>82</v>
+        <v>565</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>82</v>
@@ -17118,12 +17117,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17131,35 +17130,31 @@
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G122" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>565</v>
+        <v>106</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="O122" t="s" s="2">
         <v>569</v>
       </c>
+      <c r="N122" s="2"/>
+      <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>82</v>
       </c>
@@ -17207,7 +17202,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>570</v>
+        <v>109</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17219,7 +17214,7 @@
         <v>82</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>82</v>
@@ -17228,7 +17223,7 @@
         <v>82</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>571</v>
+        <v>82</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>82</v>
@@ -17239,10 +17234,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17253,7 +17248,7 @@
         <v>80</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>82</v>
@@ -17265,13 +17260,13 @@
         <v>82</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>504</v>
+        <v>193</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>505</v>
+        <v>194</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -17310,31 +17305,29 @@
         <v>82</v>
       </c>
       <c r="AB123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="AC123" s="2"/>
       <c r="AD123" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE123" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>82</v>
@@ -17352,14 +17345,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="124" hidden="true">
+    <row r="124">
       <c r="A124" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="C124" s="2"/>
+        <v>571</v>
+      </c>
+      <c r="C124" t="s" s="2">
+        <v>573</v>
+      </c>
       <c r="D124" t="s" s="2">
         <v>82</v>
       </c>
@@ -17368,10 +17363,10 @@
         <v>80</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H124" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I124" t="s" s="2">
         <v>82</v>
@@ -17380,15 +17375,17 @@
         <v>82</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>112</v>
+        <v>574</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>193</v>
+        <v>575</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N124" s="2"/>
+        <v>576</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>577</v>
+      </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>82</v>
@@ -17425,14 +17422,16 @@
         <v>82</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC124" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE124" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
         <v>119</v>
@@ -17444,7 +17443,7 @@
         <v>81</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
       </c>
       <c r="AJ124" t="s" s="2">
         <v>120</v>
@@ -17456,7 +17455,7 @@
         <v>82</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>82</v>
+        <v>229</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>82</v>
@@ -17465,16 +17464,14 @@
         <v>82</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="C125" t="s" s="2">
-        <v>577</v>
-      </c>
+        <v>579</v>
+      </c>
+      <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
         <v>82</v>
       </c>
@@ -17486,7 +17483,7 @@
         <v>92</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>82</v>
@@ -17495,17 +17492,15 @@
         <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>578</v>
+        <v>559</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="N125" t="s" s="2">
         <v>581</v>
       </c>
+      <c r="N125" s="2"/>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>82</v>
@@ -17554,19 +17549,19 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>119</v>
+        <v>582</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>82</v>
@@ -17575,7 +17570,7 @@
         <v>82</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>229</v>
+        <v>82</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>82</v>
@@ -17584,12 +17579,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="126" hidden="true">
+    <row r="126">
       <c r="A126" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17603,29 +17598,33 @@
         <v>92</v>
       </c>
       <c r="H126" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I126" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>565</v>
+        <v>167</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>514</v>
+        <v>586</v>
       </c>
       <c r="N126" s="2"/>
-      <c r="O126" s="2"/>
+      <c r="O126" t="s" s="2">
+        <v>587</v>
+      </c>
       <c r="P126" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q126" s="2"/>
+      <c r="Q126" t="s" s="2">
+        <v>588</v>
+      </c>
       <c r="R126" t="s" s="2">
         <v>82</v>
       </c>
@@ -17645,13 +17644,13 @@
         <v>82</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>82</v>
+        <v>589</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>82</v>
+        <v>590</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>82</v>
@@ -17669,7 +17668,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17681,7 +17680,7 @@
         <v>82</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>82</v>
@@ -17690,7 +17689,7 @@
         <v>82</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>82</v>
+        <v>592</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>82</v>
@@ -17701,10 +17700,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17712,7 +17711,7 @@
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G127" t="s" s="2">
         <v>92</v>
@@ -17721,30 +17720,28 @@
         <v>93</v>
       </c>
       <c r="I127" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J127" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>167</v>
+        <v>106</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q127" t="s" s="2">
-        <v>591</v>
-      </c>
+      <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
         <v>82</v>
       </c>
@@ -17764,13 +17761,13 @@
         <v>82</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>592</v>
+        <v>82</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>593</v>
+        <v>82</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>82</v>
@@ -17788,7 +17785,7 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17809,7 +17806,7 @@
         <v>82</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>82</v>
@@ -17820,10 +17817,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17846,24 +17843,24 @@
         <v>93</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
-        <v>82</v>
+        <v>605</v>
       </c>
       <c r="S128" t="s" s="2">
         <v>82</v>
@@ -17905,7 +17902,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -17914,7 +17911,7 @@
         <v>92</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>82</v>
+        <v>607</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>104</v>
@@ -17926,7 +17923,7 @@
         <v>82</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>82</v>
@@ -17937,10 +17934,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17963,24 +17960,26 @@
         <v>93</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="N129" s="2"/>
+        <v>611</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>612</v>
+      </c>
       <c r="O129" t="s" s="2">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q129" s="2"/>
       <c r="R129" t="s" s="2">
-        <v>608</v>
+        <v>82</v>
       </c>
       <c r="S129" t="s" s="2">
         <v>82</v>
@@ -18022,7 +18021,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -18031,7 +18030,7 @@
         <v>92</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>610</v>
+        <v>82</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>104</v>
@@ -18043,7 +18042,7 @@
         <v>82</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>82</v>
@@ -18054,18 +18053,20 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="C130" s="2"/>
+        <v>530</v>
+      </c>
+      <c r="C130" t="s" s="2">
+        <v>616</v>
+      </c>
       <c r="D130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G130" t="s" s="2">
         <v>92</v>
@@ -18080,19 +18081,19 @@
         <v>93</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>167</v>
+        <v>232</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>613</v>
+        <v>545</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>614</v>
+        <v>546</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>615</v>
+        <v>534</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>616</v>
+        <v>535</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>82</v>
@@ -18117,13 +18118,11 @@
         <v>82</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y130" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="Y130" s="2"/>
       <c r="Z130" t="s" s="2">
-        <v>82</v>
+        <v>617</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>82</v>
@@ -18141,7 +18140,7 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>617</v>
+        <v>530</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -18150,7 +18149,7 @@
         <v>92</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>82</v>
+        <v>538</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>104</v>
@@ -18159,28 +18158,26 @@
         <v>82</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>82</v>
+        <v>539</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>602</v>
+        <v>540</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>82</v>
+        <v>541</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
         <v>618</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="C131" t="s" s="2">
-        <v>619</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
         <v>82</v>
       </c>
@@ -18192,29 +18189,25 @@
         <v>92</v>
       </c>
       <c r="H131" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>232</v>
+        <v>106</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>551</v>
+        <v>107</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>541</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N131" s="2"/>
+      <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>82</v>
       </c>
@@ -18238,11 +18231,13 @@
         <v>82</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="Y131" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z131" t="s" s="2">
-        <v>620</v>
+        <v>82</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>82</v>
@@ -18260,7 +18255,7 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>536</v>
+        <v>109</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18269,44 +18264,44 @@
         <v>92</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>544</v>
+        <v>82</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>545</v>
+        <v>82</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>547</v>
+        <v>82</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>82</v>
@@ -18318,15 +18313,17 @@
         <v>82</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N132" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>82</v>
@@ -18363,31 +18360,31 @@
         <v>82</v>
       </c>
       <c r="AB132" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC132" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD132" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE132" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AK132" t="s" s="2">
         <v>82</v>
@@ -18405,46 +18402,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="133" hidden="true">
+    <row r="133">
       <c r="A133" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>556</v>
+        <v>621</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G133" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H133" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>113</v>
+        <v>247</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>114</v>
+        <v>248</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O133" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="P133" t="s" s="2">
         <v>82</v>
       </c>
@@ -18480,19 +18479,19 @@
         <v>82</v>
       </c>
       <c r="AB133" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC133" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE133" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>119</v>
+        <v>252</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18504,7 +18503,7 @@
         <v>82</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>82</v>
@@ -18513,7 +18512,7 @@
         <v>82</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>82</v>
+        <v>253</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>82</v>
@@ -18522,12 +18521,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="B134" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18535,35 +18534,31 @@
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H134" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J134" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>247</v>
+        <v>107</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N134" s="2"/>
+      <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>82</v>
       </c>
@@ -18611,19 +18606,19 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>252</v>
+        <v>109</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK134" t="s" s="2">
         <v>82</v>
@@ -18632,7 +18627,7 @@
         <v>82</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>82</v>
@@ -18643,21 +18638,21 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="B135" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="B135" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>82</v>
@@ -18669,15 +18664,17 @@
         <v>82</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N135" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>82</v>
@@ -18714,31 +18711,31 @@
         <v>82</v>
       </c>
       <c r="AB135" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC135" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE135" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AK135" t="s" s="2">
         <v>82</v>
@@ -18756,46 +18753,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="136" hidden="true">
+    <row r="136">
       <c r="A136" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="B136" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="B136" t="s" s="2">
-        <v>628</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H136" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I136" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>113</v>
+        <v>262</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>114</v>
+        <v>263</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O136" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="O136" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P136" t="s" s="2">
         <v>82</v>
       </c>
@@ -18831,31 +18830,31 @@
         <v>82</v>
       </c>
       <c r="AB136" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC136" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD136" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE136" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>119</v>
+        <v>267</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK136" t="s" s="2">
         <v>82</v>
@@ -18864,7 +18863,7 @@
         <v>82</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>82</v>
@@ -18875,10 +18874,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="B137" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="B137" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18886,7 +18885,7 @@
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G137" t="s" s="2">
         <v>92</v>
@@ -18901,20 +18900,18 @@
         <v>93</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>82</v>
       </c>
@@ -18962,7 +18959,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -18983,7 +18980,7 @@
         <v>82</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>82</v>
@@ -18994,10 +18991,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B138" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19005,7 +19002,7 @@
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G138" t="s" s="2">
         <v>92</v>
@@ -19020,18 +19017,18 @@
         <v>93</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>106</v>
+        <v>167</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O138" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="N138" s="2"/>
+      <c r="O138" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="P138" t="s" s="2">
         <v>82</v>
       </c>
@@ -19079,7 +19076,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19100,7 +19097,7 @@
         <v>82</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>82</v>
@@ -19109,12 +19106,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="B139" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="B139" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19122,13 +19119,13 @@
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G139" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H139" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I139" t="s" s="2">
         <v>82</v>
@@ -19137,17 +19134,17 @@
         <v>93</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>167</v>
+        <v>106</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>82</v>
@@ -19196,7 +19193,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19217,7 +19214,7 @@
         <v>82</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>82</v>
@@ -19228,10 +19225,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="B140" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="B140" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19254,17 +19251,19 @@
         <v>93</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>106</v>
+        <v>293</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N140" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="O140" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>82</v>
@@ -19313,7 +19312,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19334,7 +19333,7 @@
         <v>82</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>82</v>
@@ -19345,10 +19344,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="B141" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="B141" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19371,19 +19370,19 @@
         <v>93</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>293</v>
+        <v>106</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>82</v>
@@ -19432,7 +19431,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19453,7 +19452,7 @@
         <v>82</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>82</v>
@@ -19462,14 +19461,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="142" hidden="true">
+    <row r="142">
       <c r="A142" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="C142" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="B142" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
         <v>82</v>
       </c>
@@ -19481,7 +19482,7 @@
         <v>92</v>
       </c>
       <c r="H142" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I142" t="s" s="2">
         <v>82</v>
@@ -19490,19 +19491,19 @@
         <v>93</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>106</v>
+        <v>640</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>302</v>
+        <v>545</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>303</v>
+        <v>546</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>304</v>
+        <v>534</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>305</v>
+        <v>535</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>82</v>
@@ -19551,7 +19552,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>306</v>
+        <v>530</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19560,7 +19561,7 @@
         <v>92</v>
       </c>
       <c r="AI142" t="s" s="2">
-        <v>82</v>
+        <v>538</v>
       </c>
       <c r="AJ142" t="s" s="2">
         <v>104</v>
@@ -19569,16 +19570,16 @@
         <v>82</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>82</v>
+        <v>539</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>307</v>
+        <v>540</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO142" t="s" s="2">
-        <v>82</v>
+        <v>541</v>
       </c>
     </row>
     <row r="143">
@@ -19586,7 +19587,7 @@
         <v>641</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="C143" t="s" s="2">
         <v>642</v>
@@ -19614,16 +19615,16 @@
         <v>643</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>82</v>
@@ -19672,7 +19673,7 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19681,7 +19682,7 @@
         <v>92</v>
       </c>
       <c r="AI143" t="s" s="2">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="AJ143" t="s" s="2">
         <v>104</v>
@@ -19690,16 +19691,16 @@
         <v>82</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO143" t="s" s="2">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="144">
@@ -19707,11 +19708,9 @@
         <v>644</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="C144" t="s" s="2">
-        <v>645</v>
-      </c>
+        <v>644</v>
+      </c>
+      <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
         <v>82</v>
       </c>
@@ -19729,22 +19728,22 @@
         <v>82</v>
       </c>
       <c r="J144" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K144" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L144" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>646</v>
       </c>
-      <c r="L144" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="M144" t="s" s="2">
-        <v>552</v>
-      </c>
       <c r="N144" t="s" s="2">
-        <v>540</v>
+        <v>647</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>541</v>
+        <v>648</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>82</v>
@@ -19769,13 +19768,13 @@
         <v>82</v>
       </c>
       <c r="X144" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="Y144" t="s" s="2">
-        <v>82</v>
+        <v>649</v>
       </c>
       <c r="Z144" t="s" s="2">
-        <v>82</v>
+        <v>650</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>82</v>
@@ -19793,7 +19792,7 @@
         <v>82</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>536</v>
+        <v>644</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -19802,7 +19801,7 @@
         <v>92</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>544</v>
+        <v>651</v>
       </c>
       <c r="AJ144" t="s" s="2">
         <v>104</v>
@@ -19811,35 +19810,35 @@
         <v>82</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>545</v>
+        <v>82</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>546</v>
+        <v>229</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO144" t="s" s="2">
-        <v>547</v>
+        <v>82</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>82</v>
+        <v>653</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>93</v>
@@ -19854,16 +19853,16 @@
         <v>232</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>82</v>
@@ -19891,37 +19890,37 @@
         <v>149</v>
       </c>
       <c r="Y145" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="Z145" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AA145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF145" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="Z145" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="AA145" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB145" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC145" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD145" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE145" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF145" t="s" s="2">
-        <v>647</v>
-      </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>654</v>
+        <v>82</v>
       </c>
       <c r="AJ145" t="s" s="2">
         <v>104</v>
@@ -19930,28 +19929,28 @@
         <v>82</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>82</v>
+        <v>660</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>229</v>
+        <v>661</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO145" t="s" s="2">
-        <v>82</v>
+        <v>662</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>656</v>
+        <v>82</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
@@ -19970,19 +19969,19 @@
         <v>82</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>232</v>
+        <v>664</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>82</v>
@@ -20007,13 +20006,13 @@
         <v>82</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>661</v>
+        <v>82</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>662</v>
+        <v>82</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>82</v>
@@ -20031,7 +20030,7 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20049,24 +20048,24 @@
         <v>82</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>663</v>
+        <v>82</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO146" t="s" s="2">
-        <v>665</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20077,10 +20076,10 @@
         <v>80</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H147" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I147" t="s" s="2">
         <v>82</v>
@@ -20089,20 +20088,18 @@
         <v>82</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>667</v>
+        <v>232</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="O147" t="s" s="2">
-        <v>671</v>
-      </c>
+        <v>673</v>
+      </c>
+      <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>82</v>
       </c>
@@ -20126,13 +20123,13 @@
         <v>82</v>
       </c>
       <c r="X147" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>82</v>
+        <v>674</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>82</v>
+        <v>675</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>82</v>
@@ -20150,13 +20147,13 @@
         <v>82</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH147" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI147" t="s" s="2">
         <v>82</v>
@@ -20168,24 +20165,24 @@
         <v>82</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>82</v>
+        <v>676</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO147" t="s" s="2">
-        <v>82</v>
+        <v>678</v>
       </c>
     </row>
-    <row r="148" hidden="true">
+    <row r="148">
       <c r="A148" t="s" s="2">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20196,10 +20193,10 @@
         <v>80</v>
       </c>
       <c r="G148" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H148" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I148" t="s" s="2">
         <v>82</v>
@@ -20211,15 +20208,17 @@
         <v>232</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="O148" s="2"/>
+        <v>682</v>
+      </c>
+      <c r="O148" t="s" s="2">
+        <v>683</v>
+      </c>
       <c r="P148" t="s" s="2">
         <v>82</v>
       </c>
@@ -20246,10 +20245,10 @@
         <v>157</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>82</v>
@@ -20267,7 +20266,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20285,24 +20284,24 @@
         <v>82</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>679</v>
+        <v>82</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO148" t="s" s="2">
-        <v>681</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20316,7 +20315,7 @@
         <v>92</v>
       </c>
       <c r="H149" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I149" t="s" s="2">
         <v>82</v>
@@ -20325,20 +20324,16 @@
         <v>82</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>232</v>
+        <v>106</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>683</v>
+        <v>107</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>686</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N149" s="2"/>
+      <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
         <v>82</v>
       </c>
@@ -20362,13 +20357,13 @@
         <v>82</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>687</v>
+        <v>82</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>688</v>
+        <v>82</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>82</v>
@@ -20386,7 +20381,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>682</v>
+        <v>109</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20398,7 +20393,7 @@
         <v>82</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK149" t="s" s="2">
         <v>82</v>
@@ -20407,7 +20402,7 @@
         <v>82</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>689</v>
+        <v>82</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>82</v>
@@ -20418,21 +20413,21 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G150" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H150" t="s" s="2">
         <v>82</v>
@@ -20444,15 +20439,17 @@
         <v>82</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N150" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N150" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
         <v>82</v>
@@ -20489,31 +20486,31 @@
         <v>82</v>
       </c>
       <c r="AB150" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC150" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD150" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE150" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH150" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI150" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AK150" t="s" s="2">
         <v>82</v>
@@ -20531,16 +20528,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="151" hidden="true">
+    <row r="151">
       <c r="A151" t="s" s="2">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -20550,27 +20547,29 @@
         <v>81</v>
       </c>
       <c r="H151" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I151" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J151" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>113</v>
+        <v>247</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>114</v>
+        <v>248</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O151" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="O151" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="P151" t="s" s="2">
         <v>82</v>
       </c>
@@ -20606,19 +20605,19 @@
         <v>82</v>
       </c>
       <c r="AB151" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC151" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD151" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE151" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>119</v>
+        <v>252</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20630,7 +20629,7 @@
         <v>82</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK151" t="s" s="2">
         <v>82</v>
@@ -20639,7 +20638,7 @@
         <v>82</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>82</v>
+        <v>253</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>82</v>
@@ -20648,12 +20647,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20664,32 +20663,28 @@
         <v>80</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H152" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I152" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J152" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>247</v>
+        <v>107</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O152" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N152" s="2"/>
+      <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
         <v>82</v>
       </c>
@@ -20737,19 +20732,19 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>252</v>
+        <v>109</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI152" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK152" t="s" s="2">
         <v>82</v>
@@ -20758,7 +20753,7 @@
         <v>82</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>82</v>
@@ -20769,21 +20764,21 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>82</v>
@@ -20795,15 +20790,17 @@
         <v>82</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N153" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N153" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
         <v>82</v>
@@ -20840,31 +20837,31 @@
         <v>82</v>
       </c>
       <c r="AB153" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC153" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD153" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE153" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI153" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AK153" t="s" s="2">
         <v>82</v>
@@ -20882,46 +20879,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="154" hidden="true">
+    <row r="154">
       <c r="A154" t="s" s="2">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H154" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I154" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>113</v>
+        <v>262</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>114</v>
+        <v>263</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O154" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="O154" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P154" t="s" s="2">
         <v>82</v>
       </c>
@@ -20957,31 +20956,31 @@
         <v>82</v>
       </c>
       <c r="AB154" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC154" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD154" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE154" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>119</v>
+        <v>267</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH154" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI154" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK154" t="s" s="2">
         <v>82</v>
@@ -20990,7 +20989,7 @@
         <v>82</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>82</v>
@@ -20999,12 +20998,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21012,13 +21011,13 @@
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G155" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H155" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I155" t="s" s="2">
         <v>82</v>
@@ -21027,20 +21026,18 @@
         <v>93</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O155" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
         <v>82</v>
       </c>
@@ -21088,7 +21085,7 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -21109,7 +21106,7 @@
         <v>82</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>82</v>
@@ -21118,12 +21115,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="156" hidden="true">
+    <row r="156">
       <c r="A156" t="s" s="2">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21131,13 +21128,13 @@
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G156" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H156" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I156" t="s" s="2">
         <v>82</v>
@@ -21146,18 +21143,18 @@
         <v>93</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>106</v>
+        <v>167</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O156" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="N156" s="2"/>
+      <c r="O156" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="P156" t="s" s="2">
         <v>82</v>
       </c>
@@ -21205,7 +21202,7 @@
         <v>82</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -21226,7 +21223,7 @@
         <v>82</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="AN156" t="s" s="2">
         <v>82</v>
@@ -21237,10 +21234,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21248,7 +21245,7 @@
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G157" t="s" s="2">
         <v>92</v>
@@ -21263,17 +21260,17 @@
         <v>93</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>167</v>
+        <v>106</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>82</v>
@@ -21322,7 +21319,7 @@
         <v>82</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -21343,7 +21340,7 @@
         <v>82</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>82</v>
@@ -21352,12 +21349,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21371,7 +21368,7 @@
         <v>92</v>
       </c>
       <c r="H158" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I158" t="s" s="2">
         <v>82</v>
@@ -21380,17 +21377,19 @@
         <v>93</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>106</v>
+        <v>293</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N158" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="N158" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="O158" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>82</v>
@@ -21439,7 +21438,7 @@
         <v>82</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -21460,7 +21459,7 @@
         <v>82</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>82</v>
@@ -21471,10 +21470,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21497,19 +21496,19 @@
         <v>93</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>293</v>
+        <v>106</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>82</v>
@@ -21558,7 +21557,7 @@
         <v>82</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -21579,7 +21578,7 @@
         <v>82</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>82</v>
@@ -21588,12 +21587,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="160" hidden="true">
+    <row r="160">
       <c r="A160" t="s" s="2">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21607,29 +21606,27 @@
         <v>92</v>
       </c>
       <c r="H160" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I160" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J160" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>106</v>
+        <v>699</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>302</v>
+        <v>700</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>303</v>
+        <v>701</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O160" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>702</v>
+      </c>
+      <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
         <v>82</v>
       </c>
@@ -21677,7 +21674,7 @@
         <v>82</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>306</v>
+        <v>698</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -21695,24 +21692,24 @@
         <v>82</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>82</v>
+        <v>703</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>307</v>
+        <v>704</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO160" t="s" s="2">
-        <v>82</v>
+        <v>705</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21726,7 +21723,7 @@
         <v>92</v>
       </c>
       <c r="H161" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I161" t="s" s="2">
         <v>82</v>
@@ -21735,17 +21732,15 @@
         <v>82</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>702</v>
+        <v>106</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>703</v>
+        <v>107</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>705</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N161" s="2"/>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
         <v>82</v>
@@ -21794,7 +21789,7 @@
         <v>82</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>701</v>
+        <v>109</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -21806,41 +21801,41 @@
         <v>82</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK161" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>706</v>
+        <v>82</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>707</v>
+        <v>82</v>
       </c>
       <c r="AN161" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO161" t="s" s="2">
-        <v>708</v>
+        <v>82</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G162" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H162" t="s" s="2">
         <v>82</v>
@@ -21852,15 +21847,17 @@
         <v>82</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N162" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N162" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
         <v>82</v>
@@ -21897,31 +21894,31 @@
         <v>82</v>
       </c>
       <c r="AB162" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC162" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD162" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE162" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH162" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI162" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ162" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AK162" t="s" s="2">
         <v>82</v>
@@ -21939,44 +21936,44 @@
         <v>82</v>
       </c>
     </row>
-    <row r="163" hidden="true">
+    <row r="163">
       <c r="A163" t="s" s="2">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E163" s="2"/>
       <c r="F163" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H163" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I163" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J163" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>113</v>
+        <v>449</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>114</v>
+        <v>450</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>115</v>
+        <v>451</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -22014,31 +22011,31 @@
         <v>82</v>
       </c>
       <c r="AB163" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC163" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD163" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE163" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>119</v>
+        <v>452</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH163" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI163" t="s" s="2">
-        <v>82</v>
+        <v>453</v>
       </c>
       <c r="AJ163" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK163" t="s" s="2">
         <v>82</v>
@@ -22056,12 +22053,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22075,7 +22072,7 @@
         <v>92</v>
       </c>
       <c r="H164" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I164" t="s" s="2">
         <v>82</v>
@@ -22084,16 +22081,16 @@
         <v>93</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -22119,13 +22116,13 @@
         <v>82</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>82</v>
+        <v>459</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>82</v>
@@ -22143,7 +22140,7 @@
         <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -22152,7 +22149,7 @@
         <v>92</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>453</v>
+        <v>82</v>
       </c>
       <c r="AJ164" t="s" s="2">
         <v>104</v>
@@ -22173,12 +22170,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="165" hidden="true">
+    <row r="165">
       <c r="A165" t="s" s="2">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22192,7 +22189,7 @@
         <v>92</v>
       </c>
       <c r="H165" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I165" t="s" s="2">
         <v>82</v>
@@ -22201,16 +22198,16 @@
         <v>93</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>133</v>
+        <v>203</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -22236,13 +22233,13 @@
         <v>82</v>
       </c>
       <c r="X165" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>459</v>
+        <v>82</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>82</v>
@@ -22260,7 +22257,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22290,12 +22287,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22309,7 +22306,7 @@
         <v>92</v>
       </c>
       <c r="H166" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I166" t="s" s="2">
         <v>82</v>
@@ -22318,16 +22315,16 @@
         <v>93</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>203</v>
+        <v>106</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -22377,7 +22374,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22407,12 +22404,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="167" hidden="true">
+    <row r="167">
       <c r="A167" t="s" s="2">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22426,25 +22423,25 @@
         <v>92</v>
       </c>
       <c r="H167" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I167" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J167" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>106</v>
+        <v>713</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>467</v>
+        <v>714</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>468</v>
+        <v>715</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>469</v>
+        <v>716</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -22494,7 +22491,7 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>470</v>
+        <v>712</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22512,24 +22509,24 @@
         <v>82</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>82</v>
+        <v>717</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>82</v>
+        <v>718</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>82</v>
+        <v>719</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22543,7 +22540,7 @@
         <v>92</v>
       </c>
       <c r="H168" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I168" t="s" s="2">
         <v>82</v>
@@ -22552,17 +22549,15 @@
         <v>82</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>716</v>
+        <v>106</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>717</v>
+        <v>107</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>719</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N168" s="2"/>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
         <v>82</v>
@@ -22611,7 +22606,7 @@
         <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>715</v>
+        <v>109</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -22623,41 +22618,41 @@
         <v>82</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK168" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>720</v>
+        <v>82</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>721</v>
+        <v>82</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>722</v>
+        <v>82</v>
       </c>
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G169" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H169" t="s" s="2">
         <v>82</v>
@@ -22669,15 +22664,17 @@
         <v>82</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N169" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N169" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
         <v>82</v>
@@ -22714,31 +22711,31 @@
         <v>82</v>
       </c>
       <c r="AB169" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC169" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD169" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE169" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH169" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI169" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AK169" t="s" s="2">
         <v>82</v>
@@ -22756,44 +22753,44 @@
         <v>82</v>
       </c>
     </row>
-    <row r="170" hidden="true">
+    <row r="170">
       <c r="A170" t="s" s="2">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G170" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H170" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I170" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J170" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>113</v>
+        <v>449</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>114</v>
+        <v>450</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>115</v>
+        <v>451</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -22831,31 +22828,31 @@
         <v>82</v>
       </c>
       <c r="AB170" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC170" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD170" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE170" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>119</v>
+        <v>452</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH170" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI170" t="s" s="2">
-        <v>82</v>
+        <v>453</v>
       </c>
       <c r="AJ170" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK170" t="s" s="2">
         <v>82</v>
@@ -22873,12 +22870,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22892,7 +22889,7 @@
         <v>92</v>
       </c>
       <c r="H171" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I171" t="s" s="2">
         <v>82</v>
@@ -22901,16 +22898,16 @@
         <v>93</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -22936,13 +22933,13 @@
         <v>82</v>
       </c>
       <c r="X171" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="Y171" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="Z171" t="s" s="2">
-        <v>82</v>
+        <v>459</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>82</v>
@@ -22960,7 +22957,7 @@
         <v>82</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -22969,7 +22966,7 @@
         <v>92</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>453</v>
+        <v>82</v>
       </c>
       <c r="AJ171" t="s" s="2">
         <v>104</v>
@@ -22990,12 +22987,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="172" hidden="true">
+    <row r="172">
       <c r="A172" t="s" s="2">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23009,7 +23006,7 @@
         <v>92</v>
       </c>
       <c r="H172" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I172" t="s" s="2">
         <v>82</v>
@@ -23018,16 +23015,16 @@
         <v>93</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>133</v>
+        <v>203</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -23053,13 +23050,13 @@
         <v>82</v>
       </c>
       <c r="X172" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="Y172" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
       <c r="Z172" t="s" s="2">
-        <v>459</v>
+        <v>82</v>
       </c>
       <c r="AA172" t="s" s="2">
         <v>82</v>
@@ -23077,7 +23074,7 @@
         <v>82</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23107,12 +23104,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23126,7 +23123,7 @@
         <v>92</v>
       </c>
       <c r="H173" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I173" t="s" s="2">
         <v>82</v>
@@ -23135,16 +23132,16 @@
         <v>93</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>203</v>
+        <v>106</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
@@ -23194,7 +23191,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23224,12 +23221,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="174" hidden="true">
+    <row r="174">
       <c r="A174" t="s" s="2">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23240,30 +23237,32 @@
         <v>80</v>
       </c>
       <c r="G174" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H174" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I174" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J174" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>106</v>
+        <v>727</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>467</v>
+        <v>728</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>468</v>
+        <v>729</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="O174" s="2"/>
+        <v>730</v>
+      </c>
+      <c r="O174" t="s" s="2">
+        <v>731</v>
+      </c>
       <c r="P174" t="s" s="2">
         <v>82</v>
       </c>
@@ -23311,19 +23310,19 @@
         <v>82</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>470</v>
+        <v>726</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH174" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI174" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>104</v>
+        <v>732</v>
       </c>
       <c r="AK174" t="s" s="2">
         <v>82</v>
@@ -23332,7 +23331,7 @@
         <v>82</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>82</v>
+        <v>733</v>
       </c>
       <c r="AN174" t="s" s="2">
         <v>82</v>
@@ -23341,12 +23340,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23357,10 +23356,10 @@
         <v>80</v>
       </c>
       <c r="G175" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H175" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I175" t="s" s="2">
         <v>82</v>
@@ -23369,20 +23368,16 @@
         <v>82</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>730</v>
+        <v>106</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>731</v>
+        <v>107</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="O175" t="s" s="2">
-        <v>734</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N175" s="2"/>
+      <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
         <v>82</v>
       </c>
@@ -23430,19 +23425,19 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>729</v>
+        <v>109</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH175" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI175" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ175" t="s" s="2">
-        <v>735</v>
+        <v>82</v>
       </c>
       <c r="AK175" t="s" s="2">
         <v>82</v>
@@ -23451,7 +23446,7 @@
         <v>82</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>736</v>
+        <v>82</v>
       </c>
       <c r="AN175" t="s" s="2">
         <v>82</v>
@@ -23462,21 +23457,21 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H176" t="s" s="2">
         <v>82</v>
@@ -23488,15 +23483,17 @@
         <v>82</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N176" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N176" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
         <v>82</v>
@@ -23545,19 +23542,19 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI176" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AK176" t="s" s="2">
         <v>82</v>
@@ -23577,14 +23574,14 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
-        <v>111</v>
+        <v>737</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
@@ -23597,24 +23594,26 @@
         <v>82</v>
       </c>
       <c r="I177" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J177" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K177" t="s" s="2">
         <v>112</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>113</v>
+        <v>738</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>114</v>
+        <v>739</v>
       </c>
       <c r="N177" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="O177" s="2"/>
+      <c r="O177" t="s" s="2">
+        <v>740</v>
+      </c>
       <c r="P177" t="s" s="2">
         <v>82</v>
       </c>
@@ -23662,7 +23661,7 @@
         <v>82</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>119</v>
+        <v>741</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -23692,48 +23691,44 @@
         <v>82</v>
       </c>
     </row>
-    <row r="178" hidden="true">
+    <row r="178">
       <c r="A178" t="s" s="2">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
-        <v>740</v>
+        <v>82</v>
       </c>
       <c r="E178" s="2"/>
       <c r="F178" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G178" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H178" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I178" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J178" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>112</v>
+        <v>743</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="N178" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O178" t="s" s="2">
-        <v>743</v>
-      </c>
+        <v>745</v>
+      </c>
+      <c r="N178" s="2"/>
+      <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
         <v>82</v>
       </c>
@@ -23781,19 +23776,19 @@
         <v>82</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH178" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI178" t="s" s="2">
-        <v>82</v>
+        <v>746</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK178" t="s" s="2">
         <v>82</v>
@@ -23802,7 +23797,7 @@
         <v>82</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>82</v>
+        <v>747</v>
       </c>
       <c r="AN178" t="s" s="2">
         <v>82</v>
@@ -23813,10 +23808,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23839,13 +23834,13 @@
         <v>82</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
@@ -23896,7 +23891,7 @@
         <v>82</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -23905,7 +23900,7 @@
         <v>92</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="AJ179" t="s" s="2">
         <v>104</v>
@@ -23917,7 +23912,7 @@
         <v>82</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="AN179" t="s" s="2">
         <v>82</v>
@@ -23926,7 +23921,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
         <v>751</v>
       </c>
@@ -23945,7 +23940,7 @@
         <v>92</v>
       </c>
       <c r="H180" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I180" t="s" s="2">
         <v>82</v>
@@ -23954,7 +23949,7 @@
         <v>82</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>746</v>
+        <v>232</v>
       </c>
       <c r="L180" t="s" s="2">
         <v>752</v>
@@ -23962,8 +23957,12 @@
       <c r="M180" t="s" s="2">
         <v>753</v>
       </c>
-      <c r="N180" s="2"/>
-      <c r="O180" s="2"/>
+      <c r="N180" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="O180" t="s" s="2">
+        <v>755</v>
+      </c>
       <c r="P180" t="s" s="2">
         <v>82</v>
       </c>
@@ -23987,13 +23986,13 @@
         <v>82</v>
       </c>
       <c r="X180" t="s" s="2">
-        <v>82</v>
+        <v>171</v>
       </c>
       <c r="Y180" t="s" s="2">
-        <v>82</v>
+        <v>756</v>
       </c>
       <c r="Z180" t="s" s="2">
-        <v>82</v>
+        <v>757</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>82</v>
@@ -24020,7 +24019,7 @@
         <v>92</v>
       </c>
       <c r="AI180" t="s" s="2">
-        <v>749</v>
+        <v>82</v>
       </c>
       <c r="AJ180" t="s" s="2">
         <v>104</v>
@@ -24029,10 +24028,10 @@
         <v>82</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>82</v>
+        <v>758</v>
       </c>
       <c r="AM180" t="s" s="2">
-        <v>750</v>
+        <v>759</v>
       </c>
       <c r="AN180" t="s" s="2">
         <v>82</v>
@@ -24043,10 +24042,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24057,7 +24056,7 @@
         <v>80</v>
       </c>
       <c r="G181" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H181" t="s" s="2">
         <v>82</v>
@@ -24072,16 +24071,16 @@
         <v>232</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>757</v>
+        <v>763</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>758</v>
+        <v>764</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>82</v>
@@ -24106,37 +24105,37 @@
         <v>82</v>
       </c>
       <c r="X181" t="s" s="2">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="Y181" t="s" s="2">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="Z181" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="AA181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE181" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF181" t="s" s="2">
         <v>760</v>
       </c>
-      <c r="AA181" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB181" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC181" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD181" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE181" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF181" t="s" s="2">
-        <v>754</v>
-      </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH181" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI181" t="s" s="2">
         <v>82</v>
@@ -24148,10 +24147,10 @@
         <v>82</v>
       </c>
       <c r="AL181" t="s" s="2">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="AM181" t="s" s="2">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="AN181" t="s" s="2">
         <v>82</v>
@@ -24162,10 +24161,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24176,7 +24175,7 @@
         <v>80</v>
       </c>
       <c r="G182" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H182" t="s" s="2">
         <v>82</v>
@@ -24188,19 +24187,17 @@
         <v>82</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>232</v>
+        <v>640</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>765</v>
-      </c>
-      <c r="N182" t="s" s="2">
-        <v>766</v>
-      </c>
+        <v>769</v>
+      </c>
+      <c r="N182" s="2"/>
       <c r="O182" t="s" s="2">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>82</v>
@@ -24225,13 +24222,13 @@
         <v>82</v>
       </c>
       <c r="X182" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="Y182" t="s" s="2">
-        <v>768</v>
+        <v>82</v>
       </c>
       <c r="Z182" t="s" s="2">
-        <v>769</v>
+        <v>82</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>82</v>
@@ -24249,13 +24246,13 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH182" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI182" t="s" s="2">
         <v>82</v>
@@ -24267,10 +24264,10 @@
         <v>82</v>
       </c>
       <c r="AL182" t="s" s="2">
-        <v>761</v>
+        <v>82</v>
       </c>
       <c r="AM182" t="s" s="2">
-        <v>762</v>
+        <v>82</v>
       </c>
       <c r="AN182" t="s" s="2">
         <v>82</v>
@@ -24281,10 +24278,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24307,18 +24304,16 @@
         <v>82</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>643</v>
+        <v>106</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="N183" s="2"/>
-      <c r="O183" t="s" s="2">
-        <v>773</v>
-      </c>
+      <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
         <v>82</v>
       </c>
@@ -24366,7 +24361,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -24387,7 +24382,7 @@
         <v>82</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>82</v>
+        <v>747</v>
       </c>
       <c r="AN183" t="s" s="2">
         <v>82</v>
@@ -24412,7 +24407,7 @@
         <v>80</v>
       </c>
       <c r="G184" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H184" t="s" s="2">
         <v>82</v>
@@ -24421,18 +24416,20 @@
         <v>82</v>
       </c>
       <c r="J184" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>106</v>
+        <v>775</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>776</v>
-      </c>
-      <c r="N184" s="2"/>
+        <v>777</v>
+      </c>
+      <c r="N184" t="s" s="2">
+        <v>778</v>
+      </c>
       <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
         <v>82</v>
@@ -24487,7 +24484,7 @@
         <v>80</v>
       </c>
       <c r="AH184" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI184" t="s" s="2">
         <v>82</v>
@@ -24502,7 +24499,7 @@
         <v>82</v>
       </c>
       <c r="AM184" t="s" s="2">
-        <v>750</v>
+        <v>779</v>
       </c>
       <c r="AN184" t="s" s="2">
         <v>82</v>
@@ -24513,10 +24510,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24539,16 +24536,16 @@
         <v>93</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
@@ -24598,7 +24595,7 @@
         <v>82</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -24619,7 +24616,7 @@
         <v>82</v>
       </c>
       <c r="AM185" t="s" s="2">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="AN185" t="s" s="2">
         <v>82</v>
@@ -24630,10 +24627,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -24656,18 +24653,20 @@
         <v>93</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>784</v>
+        <v>727</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>787</v>
-      </c>
-      <c r="O186" s="2"/>
+        <v>788</v>
+      </c>
+      <c r="O186" t="s" s="2">
+        <v>789</v>
+      </c>
       <c r="P186" t="s" s="2">
         <v>82</v>
       </c>
@@ -24715,7 +24714,7 @@
         <v>82</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -24736,7 +24735,7 @@
         <v>82</v>
       </c>
       <c r="AM186" t="s" s="2">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="AN186" t="s" s="2">
         <v>82</v>
@@ -24747,10 +24746,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -24761,7 +24760,7 @@
         <v>80</v>
       </c>
       <c r="G187" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H187" t="s" s="2">
         <v>82</v>
@@ -24770,23 +24769,19 @@
         <v>82</v>
       </c>
       <c r="J187" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>730</v>
+        <v>106</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>789</v>
+        <v>107</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>790</v>
-      </c>
-      <c r="N187" t="s" s="2">
-        <v>791</v>
-      </c>
-      <c r="O187" t="s" s="2">
-        <v>792</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N187" s="2"/>
+      <c r="O187" s="2"/>
       <c r="P187" t="s" s="2">
         <v>82</v>
       </c>
@@ -24834,19 +24829,19 @@
         <v>82</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>788</v>
+        <v>109</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH187" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI187" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ187" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK187" t="s" s="2">
         <v>82</v>
@@ -24855,7 +24850,7 @@
         <v>82</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>793</v>
+        <v>82</v>
       </c>
       <c r="AN187" t="s" s="2">
         <v>82</v>
@@ -24866,21 +24861,21 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E188" s="2"/>
       <c r="F188" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G188" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H188" t="s" s="2">
         <v>82</v>
@@ -24892,15 +24887,17 @@
         <v>82</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N188" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N188" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
         <v>82</v>
@@ -24949,19 +24946,19 @@
         <v>82</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH188" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI188" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ188" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AK188" t="s" s="2">
         <v>82</v>
@@ -24981,14 +24978,14 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
-        <v>111</v>
+        <v>737</v>
       </c>
       <c r="E189" s="2"/>
       <c r="F189" t="s" s="2">
@@ -25001,24 +24998,26 @@
         <v>82</v>
       </c>
       <c r="I189" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J189" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K189" t="s" s="2">
         <v>112</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>113</v>
+        <v>738</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>114</v>
+        <v>739</v>
       </c>
       <c r="N189" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="O189" s="2"/>
+      <c r="O189" t="s" s="2">
+        <v>740</v>
+      </c>
       <c r="P189" t="s" s="2">
         <v>82</v>
       </c>
@@ -25066,7 +25065,7 @@
         <v>82</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>119</v>
+        <v>741</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>80</v>
@@ -25098,45 +25097,45 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
-        <v>740</v>
+        <v>82</v>
       </c>
       <c r="E190" s="2"/>
       <c r="F190" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G190" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H190" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I190" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J190" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>112</v>
+        <v>232</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>741</v>
+        <v>795</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>742</v>
+        <v>796</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>115</v>
+        <v>797</v>
       </c>
       <c r="O190" t="s" s="2">
-        <v>743</v>
+        <v>406</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>82</v>
@@ -25161,13 +25160,13 @@
         <v>82</v>
       </c>
       <c r="X190" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="Y190" t="s" s="2">
-        <v>82</v>
+        <v>407</v>
       </c>
       <c r="Z190" t="s" s="2">
-        <v>82</v>
+        <v>408</v>
       </c>
       <c r="AA190" t="s" s="2">
         <v>82</v>
@@ -25185,31 +25184,31 @@
         <v>82</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>744</v>
+        <v>794</v>
       </c>
       <c r="AG190" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH190" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI190" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ190" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK190" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL190" t="s" s="2">
-        <v>82</v>
+        <v>798</v>
       </c>
       <c r="AM190" t="s" s="2">
-        <v>82</v>
+        <v>411</v>
       </c>
       <c r="AN190" t="s" s="2">
-        <v>82</v>
+        <v>412</v>
       </c>
       <c r="AO190" t="s" s="2">
         <v>82</v>
@@ -25217,10 +25216,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25228,7 +25227,7 @@
       </c>
       <c r="E191" s="2"/>
       <c r="F191" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G191" t="s" s="2">
         <v>92</v>
@@ -25243,19 +25242,19 @@
         <v>93</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>232</v>
+        <v>800</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>799</v>
+        <v>546</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>406</v>
+        <v>535</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>82</v>
@@ -25280,13 +25279,13 @@
         <v>82</v>
       </c>
       <c r="X191" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="Y191" t="s" s="2">
-        <v>407</v>
+        <v>82</v>
       </c>
       <c r="Z191" t="s" s="2">
-        <v>408</v>
+        <v>82</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>82</v>
@@ -25304,10 +25303,10 @@
         <v>82</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="AG191" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH191" t="s" s="2">
         <v>92</v>
@@ -25322,24 +25321,24 @@
         <v>82</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="AM191" t="s" s="2">
-        <v>411</v>
+        <v>540</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="AO191" t="s" s="2">
-        <v>82</v>
+        <v>541</v>
       </c>
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25359,22 +25358,22 @@
         <v>82</v>
       </c>
       <c r="J192" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>803</v>
+        <v>232</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>552</v>
+        <v>806</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>541</v>
+        <v>648</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>82</v>
@@ -25399,13 +25398,13 @@
         <v>82</v>
       </c>
       <c r="X192" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="Y192" t="s" s="2">
-        <v>82</v>
+        <v>649</v>
       </c>
       <c r="Z192" t="s" s="2">
-        <v>82</v>
+        <v>650</v>
       </c>
       <c r="AA192" t="s" s="2">
         <v>82</v>
@@ -25423,7 +25422,7 @@
         <v>82</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>80</v>
@@ -25432,7 +25431,7 @@
         <v>92</v>
       </c>
       <c r="AI192" t="s" s="2">
-        <v>82</v>
+        <v>651</v>
       </c>
       <c r="AJ192" t="s" s="2">
         <v>104</v>
@@ -25441,35 +25440,35 @@
         <v>82</v>
       </c>
       <c r="AL192" t="s" s="2">
-        <v>806</v>
+        <v>82</v>
       </c>
       <c r="AM192" t="s" s="2">
-        <v>546</v>
+        <v>229</v>
       </c>
       <c r="AN192" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO192" t="s" s="2">
-        <v>547</v>
+        <v>82</v>
       </c>
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
-        <v>82</v>
+        <v>653</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G193" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H193" t="s" s="2">
         <v>82</v>
@@ -25484,16 +25483,16 @@
         <v>232</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>810</v>
+        <v>656</v>
       </c>
       <c r="O193" t="s" s="2">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="P193" t="s" s="2">
         <v>82</v>
@@ -25521,10 +25520,10 @@
         <v>149</v>
       </c>
       <c r="Y193" t="s" s="2">
-        <v>652</v>
+        <v>811</v>
       </c>
       <c r="Z193" t="s" s="2">
-        <v>653</v>
+        <v>812</v>
       </c>
       <c r="AA193" t="s" s="2">
         <v>82</v>
@@ -25542,16 +25541,16 @@
         <v>82</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH193" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI193" t="s" s="2">
-        <v>654</v>
+        <v>82</v>
       </c>
       <c r="AJ193" t="s" s="2">
         <v>104</v>
@@ -25560,28 +25559,28 @@
         <v>82</v>
       </c>
       <c r="AL193" t="s" s="2">
-        <v>82</v>
+        <v>660</v>
       </c>
       <c r="AM193" t="s" s="2">
-        <v>229</v>
+        <v>661</v>
       </c>
       <c r="AN193" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO193" t="s" s="2">
-        <v>82</v>
+        <v>662</v>
       </c>
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
-        <v>656</v>
+        <v>82</v>
       </c>
       <c r="E194" s="2"/>
       <c r="F194" t="s" s="2">
@@ -25600,19 +25599,19 @@
         <v>82</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>232</v>
+        <v>82</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>659</v>
+        <v>730</v>
       </c>
       <c r="O194" t="s" s="2">
-        <v>660</v>
+        <v>731</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>82</v>
@@ -25637,13 +25636,13 @@
         <v>82</v>
       </c>
       <c r="X194" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="Y194" t="s" s="2">
-        <v>814</v>
+        <v>82</v>
       </c>
       <c r="Z194" t="s" s="2">
-        <v>815</v>
+        <v>82</v>
       </c>
       <c r="AA194" t="s" s="2">
         <v>82</v>
@@ -25661,7 +25660,7 @@
         <v>82</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
@@ -25679,139 +25678,20 @@
         <v>82</v>
       </c>
       <c r="AL194" t="s" s="2">
-        <v>663</v>
+        <v>82</v>
       </c>
       <c r="AM194" t="s" s="2">
-        <v>664</v>
+        <v>733</v>
       </c>
       <c r="AN194" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO194" t="s" s="2">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="195" hidden="true">
-      <c r="A195" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="B195" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="C195" s="2"/>
-      <c r="D195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E195" s="2"/>
-      <c r="F195" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K195" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L195" t="s" s="2">
-        <v>817</v>
-      </c>
-      <c r="M195" t="s" s="2">
-        <v>818</v>
-      </c>
-      <c r="N195" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="O195" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="P195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q195" s="2"/>
-      <c r="R195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF195" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="AG195" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ195" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM195" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="AN195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO195" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO195">
+  <autoFilter ref="A1:AO194">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -25821,7 +25701,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI194">
+  <conditionalFormatting sqref="A2:AI193">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T11:58:12+00:00</t>
+    <t>2026-10-13T12:04:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T12:04:10+00:00</t>
+    <t>2026-10-13T12:10:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T12:10:53+00:00</t>
+    <t>2026-10-13T12:17:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T12:17:17+00:00</t>
+    <t>2026-10-13T12:41:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T12:41:55+00:00</t>
+    <t>2026-10-13T13:04:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
